--- a/pyramidingnew.xlsx
+++ b/pyramidingnew.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1121" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1120" uniqueCount="137">
   <si>
     <t>Count</t>
   </si>
@@ -2545,14 +2545,14 @@
         <v>1</v>
       </c>
       <c r="B44" s="18">
-        <v>46027</v>
+        <v>46119</v>
       </c>
       <c r="C44" s="4">
-        <v>92</v>
+        <v>1</v>
       </c>
       <c r="D44" s="11"/>
-      <c r="E44" s="19" t="s">
-        <v>108</v>
+      <c r="E44" s="27" t="s">
+        <v>136</v>
       </c>
       <c r="F44" s="13" t="s">
         <v>90</v>
@@ -2561,10 +2561,10 @@
         <v>2</v>
       </c>
       <c r="H44" s="19">
-        <v>952.96</v>
-      </c>
-      <c r="I44" s="4" t="s">
-        <v>93</v>
+        <v>1105</v>
+      </c>
+      <c r="I44" s="4" t="e">
+        <v>#N/A</v>
       </c>
       <c r="K44" s="6"/>
       <c r="L44" s="4"/>
@@ -2579,23 +2579,23 @@
         <v>1</v>
       </c>
       <c r="B45" s="18">
-        <v>45968</v>
+        <v>46027</v>
       </c>
       <c r="C45" s="4">
-        <v>151</v>
+        <v>92</v>
       </c>
       <c r="D45" s="11"/>
-      <c r="E45" s="20" t="s">
-        <v>28</v>
+      <c r="E45" s="19" t="s">
+        <v>108</v>
       </c>
       <c r="F45" s="13" t="s">
         <v>90</v>
       </c>
       <c r="G45" s="19">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="H45" s="19">
-        <v>126</v>
+        <v>952.96</v>
       </c>
       <c r="I45" s="4" t="s">
         <v>93</v>
@@ -2613,10 +2613,10 @@
         <v>1</v>
       </c>
       <c r="B46" s="18">
-        <v>46013</v>
+        <v>45968</v>
       </c>
       <c r="C46" s="4">
-        <v>106</v>
+        <v>151</v>
       </c>
       <c r="D46" s="11"/>
       <c r="E46" s="20" t="s">
@@ -2626,10 +2626,10 @@
         <v>90</v>
       </c>
       <c r="G46" s="19">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H46" s="19">
-        <v>132.37</v>
+        <v>126</v>
       </c>
       <c r="I46" s="4" t="s">
         <v>93</v>
@@ -2647,13 +2647,13 @@
         <v>1</v>
       </c>
       <c r="B47" s="18">
-        <v>46014</v>
+        <v>46013</v>
       </c>
       <c r="C47" s="4">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D47" s="11"/>
-      <c r="E47" s="19" t="s">
+      <c r="E47" s="20" t="s">
         <v>28</v>
       </c>
       <c r="F47" s="13" t="s">
@@ -2663,7 +2663,7 @@
         <v>19</v>
       </c>
       <c r="H47" s="19">
-        <v>139.49</v>
+        <v>132.37</v>
       </c>
       <c r="I47" s="4" t="s">
         <v>93</v>
@@ -2681,10 +2681,10 @@
         <v>1</v>
       </c>
       <c r="B48" s="18">
-        <v>46015</v>
+        <v>46014</v>
       </c>
       <c r="C48" s="4">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D48" s="11"/>
       <c r="E48" s="19" t="s">
@@ -2697,7 +2697,7 @@
         <v>19</v>
       </c>
       <c r="H48" s="19">
-        <v>145.94999999999999</v>
+        <v>139.49</v>
       </c>
       <c r="I48" s="4" t="s">
         <v>93</v>
@@ -2728,10 +2728,10 @@
         <v>90</v>
       </c>
       <c r="G49" s="19">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H49" s="19">
-        <v>153.19999999999999</v>
+        <v>145.94999999999999</v>
       </c>
       <c r="I49" s="4" t="s">
         <v>93</v>
@@ -2749,26 +2749,26 @@
         <v>1</v>
       </c>
       <c r="B50" s="18">
-        <v>45988</v>
+        <v>46015</v>
       </c>
       <c r="C50" s="4">
-        <v>131</v>
+        <v>104</v>
       </c>
       <c r="D50" s="11"/>
       <c r="E50" s="19" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
       <c r="F50" s="13" t="s">
         <v>90</v>
       </c>
       <c r="G50" s="19">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="H50" s="19">
-        <v>669</v>
-      </c>
-      <c r="I50" s="4" t="e">
-        <v>#N/A</v>
+        <v>153.19999999999999</v>
+      </c>
+      <c r="I50" s="4" t="s">
+        <v>93</v>
       </c>
       <c r="K50" s="6"/>
       <c r="L50" s="4"/>
@@ -2783,10 +2783,10 @@
         <v>1</v>
       </c>
       <c r="B51" s="18">
-        <v>45989</v>
+        <v>45988</v>
       </c>
       <c r="C51" s="4">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D51" s="11"/>
       <c r="E51" s="19" t="s">
@@ -2799,7 +2799,7 @@
         <v>4</v>
       </c>
       <c r="H51" s="19">
-        <v>638</v>
+        <v>669</v>
       </c>
       <c r="I51" s="4" t="e">
         <v>#N/A</v>
@@ -2817,10 +2817,10 @@
         <v>1</v>
       </c>
       <c r="B52" s="18">
-        <v>46002</v>
+        <v>45989</v>
       </c>
       <c r="C52" s="4">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="D52" s="11"/>
       <c r="E52" s="19" t="s">
@@ -2833,7 +2833,7 @@
         <v>4</v>
       </c>
       <c r="H52" s="19">
-        <v>701.75</v>
+        <v>638</v>
       </c>
       <c r="I52" s="4" t="e">
         <v>#N/A</v>
@@ -2867,7 +2867,7 @@
         <v>4</v>
       </c>
       <c r="H53" s="19">
-        <v>736.9</v>
+        <v>701.75</v>
       </c>
       <c r="I53" s="4" t="e">
         <v>#N/A</v>
@@ -2885,26 +2885,26 @@
         <v>1</v>
       </c>
       <c r="B54" s="18">
-        <v>46101</v>
+        <v>46002</v>
       </c>
       <c r="C54" s="4">
-        <v>18</v>
+        <v>117</v>
       </c>
       <c r="D54" s="11"/>
       <c r="E54" s="19" t="s">
-        <v>134</v>
+        <v>66</v>
       </c>
       <c r="F54" s="13" t="s">
         <v>90</v>
       </c>
       <c r="G54" s="19">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H54" s="19">
-        <v>1070.78</v>
-      </c>
-      <c r="I54" s="4" t="s">
-        <v>93</v>
+        <v>736.9</v>
+      </c>
+      <c r="I54" s="4" t="e">
+        <v>#N/A</v>
       </c>
       <c r="K54" s="6"/>
       <c r="L54" s="4"/>
@@ -2919,10 +2919,10 @@
         <v>1</v>
       </c>
       <c r="B55" s="18">
-        <v>46104</v>
+        <v>46101</v>
       </c>
       <c r="C55" s="4">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D55" s="11"/>
       <c r="E55" s="19" t="s">
@@ -2935,7 +2935,7 @@
         <v>2</v>
       </c>
       <c r="H55" s="19">
-        <v>1075.9000000000001</v>
+        <v>1070.78</v>
       </c>
       <c r="I55" s="4" t="s">
         <v>93</v>
@@ -2953,23 +2953,23 @@
         <v>1</v>
       </c>
       <c r="B56" s="18">
-        <v>45960</v>
+        <v>46104</v>
       </c>
       <c r="C56" s="4">
-        <v>159</v>
+        <v>15</v>
       </c>
       <c r="D56" s="11"/>
-      <c r="E56" s="20" t="s">
-        <v>21</v>
+      <c r="E56" s="19" t="s">
+        <v>134</v>
       </c>
       <c r="F56" s="13" t="s">
         <v>90</v>
       </c>
       <c r="G56" s="19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H56" s="19">
-        <v>836.8</v>
+        <v>1075.9000000000001</v>
       </c>
       <c r="I56" s="4" t="s">
         <v>93</v>
@@ -2987,26 +2987,26 @@
         <v>1</v>
       </c>
       <c r="B57" s="18">
-        <v>46024</v>
+        <v>46119</v>
       </c>
       <c r="C57" s="4">
-        <v>95</v>
+        <v>1</v>
       </c>
       <c r="D57" s="11"/>
-      <c r="E57" s="19" t="s">
-        <v>105</v>
+      <c r="E57" s="27" t="s">
+        <v>134</v>
       </c>
       <c r="F57" s="13" t="s">
         <v>90</v>
       </c>
       <c r="G57" s="19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H57" s="19">
-        <v>1782</v>
+        <v>1128.9000000000001</v>
       </c>
       <c r="I57" s="4" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="K57" s="6"/>
       <c r="L57" s="4"/>
@@ -3021,23 +3021,23 @@
         <v>1</v>
       </c>
       <c r="B58" s="18">
-        <v>46077</v>
+        <v>45960</v>
       </c>
       <c r="C58" s="4">
-        <v>42</v>
+        <v>159</v>
       </c>
       <c r="D58" s="11"/>
-      <c r="E58" s="19" t="s">
-        <v>27</v>
+      <c r="E58" s="20" t="s">
+        <v>21</v>
       </c>
       <c r="F58" s="13" t="s">
         <v>90</v>
       </c>
       <c r="G58" s="19">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="H58" s="19">
-        <v>194.55</v>
+        <v>836.8</v>
       </c>
       <c r="I58" s="4" t="s">
         <v>93</v>
@@ -3055,14 +3055,14 @@
         <v>1</v>
       </c>
       <c r="B59" s="18">
-        <v>46099</v>
+        <v>46024</v>
       </c>
       <c r="C59" s="4">
-        <v>20</v>
+        <v>95</v>
       </c>
       <c r="D59" s="11"/>
       <c r="E59" s="19" t="s">
-        <v>133</v>
+        <v>105</v>
       </c>
       <c r="F59" s="13" t="s">
         <v>90</v>
@@ -3071,10 +3071,10 @@
         <v>1</v>
       </c>
       <c r="H59" s="19">
-        <v>1660</v>
-      </c>
-      <c r="I59" s="4" t="e">
-        <v>#N/A</v>
+        <v>1782</v>
+      </c>
+      <c r="I59" s="4" t="s">
+        <v>95</v>
       </c>
       <c r="K59" s="6"/>
       <c r="L59" s="4"/>
@@ -3089,26 +3089,26 @@
         <v>1</v>
       </c>
       <c r="B60" s="18">
-        <v>46101</v>
+        <v>46077</v>
       </c>
       <c r="C60" s="4">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="D60" s="11"/>
       <c r="E60" s="19" t="s">
-        <v>133</v>
+        <v>27</v>
       </c>
       <c r="F60" s="13" t="s">
         <v>90</v>
       </c>
       <c r="G60" s="19">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="H60" s="19">
-        <v>1660</v>
-      </c>
-      <c r="I60" s="4" t="e">
-        <v>#N/A</v>
+        <v>194.55</v>
+      </c>
+      <c r="I60" s="4" t="s">
+        <v>93</v>
       </c>
       <c r="K60" s="6"/>
       <c r="L60" s="4"/>
@@ -3123,26 +3123,26 @@
         <v>1</v>
       </c>
       <c r="B61" s="18">
-        <v>45967</v>
+        <v>46099</v>
       </c>
       <c r="C61" s="4">
-        <v>152</v>
+        <v>20</v>
       </c>
       <c r="D61" s="11"/>
       <c r="E61" s="19" t="s">
-        <v>44</v>
+        <v>133</v>
       </c>
       <c r="F61" s="13" t="s">
         <v>90</v>
       </c>
       <c r="G61" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H61" s="19">
-        <v>1478</v>
-      </c>
-      <c r="I61" s="4" t="s">
-        <v>93</v>
+        <v>1660</v>
+      </c>
+      <c r="I61" s="4" t="e">
+        <v>#N/A</v>
       </c>
       <c r="K61" s="6"/>
       <c r="L61" s="4"/>
@@ -3157,14 +3157,14 @@
         <v>1</v>
       </c>
       <c r="B62" s="18">
-        <v>45974</v>
+        <v>46101</v>
       </c>
       <c r="C62" s="4">
-        <v>145</v>
+        <v>18</v>
       </c>
       <c r="D62" s="11"/>
-      <c r="E62" s="20" t="s">
-        <v>44</v>
+      <c r="E62" s="19" t="s">
+        <v>133</v>
       </c>
       <c r="F62" s="13" t="s">
         <v>90</v>
@@ -3172,11 +3172,11 @@
       <c r="G62" s="19">
         <v>1</v>
       </c>
-      <c r="H62" s="4">
-        <v>1630</v>
-      </c>
-      <c r="I62" s="4" t="s">
-        <v>93</v>
+      <c r="H62" s="19">
+        <v>1660</v>
+      </c>
+      <c r="I62" s="4" t="e">
+        <v>#N/A</v>
       </c>
       <c r="K62" s="6"/>
       <c r="L62" s="4"/>
@@ -3191,23 +3191,23 @@
         <v>1</v>
       </c>
       <c r="B63" s="18">
-        <v>45975</v>
+        <v>45967</v>
       </c>
       <c r="C63" s="4">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="D63" s="11"/>
-      <c r="E63" s="4" t="s">
+      <c r="E63" s="19" t="s">
         <v>44</v>
       </c>
       <c r="F63" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="G63" s="20">
-        <v>1</v>
+      <c r="G63" s="19">
+        <v>2</v>
       </c>
       <c r="H63" s="19">
-        <v>1710</v>
+        <v>1478</v>
       </c>
       <c r="I63" s="4" t="s">
         <v>93</v>
@@ -3225,23 +3225,23 @@
         <v>1</v>
       </c>
       <c r="B64" s="18">
-        <v>46062</v>
+        <v>45974</v>
       </c>
       <c r="C64" s="4">
-        <v>57</v>
+        <v>145</v>
       </c>
       <c r="D64" s="11"/>
-      <c r="E64" s="19" t="s">
+      <c r="E64" s="20" t="s">
         <v>44</v>
       </c>
       <c r="F64" s="13" t="s">
         <v>90</v>
       </c>
       <c r="G64" s="19">
-        <v>2</v>
-      </c>
-      <c r="H64" s="19">
-        <v>1533.6</v>
+        <v>1</v>
+      </c>
+      <c r="H64" s="4">
+        <v>1630</v>
       </c>
       <c r="I64" s="4" t="s">
         <v>93</v>
@@ -3259,23 +3259,23 @@
         <v>1</v>
       </c>
       <c r="B65" s="18">
-        <v>46106</v>
+        <v>45975</v>
       </c>
       <c r="C65" s="4">
-        <v>1</v>
+        <v>144</v>
       </c>
       <c r="D65" s="11"/>
-      <c r="E65" s="19" t="s">
+      <c r="E65" s="4" t="s">
         <v>44</v>
       </c>
       <c r="F65" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="G65" s="19">
+      <c r="G65" s="20">
         <v>1</v>
       </c>
       <c r="H65" s="19">
-        <v>1798.3</v>
+        <v>1710</v>
       </c>
       <c r="I65" s="4" t="s">
         <v>93</v>
@@ -3293,10 +3293,10 @@
         <v>1</v>
       </c>
       <c r="B66" s="18">
-        <v>46113</v>
+        <v>46062</v>
       </c>
       <c r="C66" s="4">
-        <v>1</v>
+        <v>57</v>
       </c>
       <c r="D66" s="11"/>
       <c r="E66" s="19" t="s">
@@ -3306,10 +3306,10 @@
         <v>90</v>
       </c>
       <c r="G66" s="19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H66" s="19">
-        <v>1890</v>
+        <v>1533.6</v>
       </c>
       <c r="I66" s="4" t="s">
         <v>93</v>
@@ -3327,23 +3327,23 @@
         <v>1</v>
       </c>
       <c r="B67" s="18">
-        <v>45992</v>
+        <v>46106</v>
       </c>
       <c r="C67" s="4">
-        <v>127</v>
+        <v>1</v>
       </c>
       <c r="D67" s="11"/>
       <c r="E67" s="19" t="s">
-        <v>71</v>
+        <v>44</v>
       </c>
       <c r="F67" s="13" t="s">
         <v>90</v>
       </c>
       <c r="G67" s="19">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H67" s="19">
-        <v>283</v>
+        <v>1798.3</v>
       </c>
       <c r="I67" s="4" t="s">
         <v>93</v>
@@ -3361,23 +3361,23 @@
         <v>1</v>
       </c>
       <c r="B68" s="18">
-        <v>46020</v>
+        <v>46113</v>
       </c>
       <c r="C68" s="4">
-        <v>99</v>
+        <v>1</v>
       </c>
       <c r="D68" s="11"/>
       <c r="E68" s="19" t="s">
-        <v>71</v>
+        <v>44</v>
       </c>
       <c r="F68" s="13" t="s">
         <v>90</v>
       </c>
       <c r="G68" s="19">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H68" s="19">
-        <v>297.3</v>
+        <v>1890</v>
       </c>
       <c r="I68" s="4" t="s">
         <v>93</v>
@@ -3395,23 +3395,23 @@
         <v>1</v>
       </c>
       <c r="B69" s="18">
-        <v>46034</v>
+        <v>45992</v>
       </c>
       <c r="C69" s="4">
-        <v>85</v>
+        <v>127</v>
       </c>
       <c r="D69" s="11"/>
       <c r="E69" s="19" t="s">
-        <v>121</v>
+        <v>71</v>
       </c>
       <c r="F69" s="13" t="s">
         <v>90</v>
       </c>
       <c r="G69" s="19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H69" s="19">
-        <v>292.10000000000002</v>
+        <v>283</v>
       </c>
       <c r="I69" s="4" t="s">
         <v>93</v>
@@ -3429,23 +3429,23 @@
         <v>1</v>
       </c>
       <c r="B70" s="18">
-        <v>46106</v>
+        <v>46020</v>
       </c>
       <c r="C70" s="4">
-        <v>1</v>
+        <v>99</v>
       </c>
       <c r="D70" s="11"/>
       <c r="E70" s="19" t="s">
-        <v>135</v>
+        <v>71</v>
       </c>
       <c r="F70" s="13" t="s">
         <v>90</v>
       </c>
       <c r="G70" s="19">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H70" s="19">
-        <v>1582.1</v>
+        <v>297.3</v>
       </c>
       <c r="I70" s="4" t="s">
         <v>93</v>
@@ -3463,26 +3463,26 @@
         <v>1</v>
       </c>
       <c r="B71" s="18">
-        <v>46006</v>
+        <v>46034</v>
       </c>
       <c r="C71" s="4">
-        <v>113</v>
+        <v>85</v>
       </c>
       <c r="D71" s="11"/>
-      <c r="E71" s="20" t="s">
-        <v>77</v>
+      <c r="E71" s="19" t="s">
+        <v>121</v>
       </c>
       <c r="F71" s="13" t="s">
         <v>90</v>
       </c>
       <c r="G71" s="19">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H71" s="19">
-        <v>262</v>
+        <v>292.10000000000002</v>
       </c>
       <c r="I71" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K71" s="6"/>
       <c r="L71" s="4"/>
@@ -3497,26 +3497,26 @@
         <v>1</v>
       </c>
       <c r="B72" s="18">
-        <v>46042</v>
+        <v>46106</v>
       </c>
       <c r="C72" s="4">
-        <v>77</v>
+        <v>1</v>
       </c>
       <c r="D72" s="11"/>
       <c r="E72" s="19" t="s">
-        <v>77</v>
+        <v>135</v>
       </c>
       <c r="F72" s="13" t="s">
         <v>90</v>
       </c>
       <c r="G72" s="19">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H72" s="19">
-        <v>275.05</v>
+        <v>1582.1</v>
       </c>
       <c r="I72" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K72" s="6"/>
       <c r="L72" s="4"/>
@@ -3531,23 +3531,23 @@
         <v>1</v>
       </c>
       <c r="B73" s="18">
-        <v>46051</v>
+        <v>46006</v>
       </c>
       <c r="C73" s="4">
-        <v>1</v>
+        <v>113</v>
       </c>
       <c r="D73" s="11"/>
-      <c r="E73" s="19" t="s">
+      <c r="E73" s="20" t="s">
         <v>77</v>
       </c>
       <c r="F73" s="13" t="s">
         <v>90</v>
       </c>
       <c r="G73" s="19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H73" s="19">
-        <v>288.05</v>
+        <v>262</v>
       </c>
       <c r="I73" s="4" t="s">
         <v>94</v>
@@ -3565,26 +3565,26 @@
         <v>1</v>
       </c>
       <c r="B74" s="18">
-        <v>46036</v>
+        <v>46042</v>
       </c>
       <c r="C74" s="4">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="D74" s="11"/>
       <c r="E74" s="19" t="s">
-        <v>118</v>
+        <v>77</v>
       </c>
       <c r="F74" s="13" t="s">
         <v>90</v>
       </c>
       <c r="G74" s="19">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H74" s="19">
-        <v>166.9</v>
+        <v>275.05</v>
       </c>
       <c r="I74" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K74" s="6"/>
       <c r="L74" s="4"/>
@@ -3599,26 +3599,26 @@
         <v>1</v>
       </c>
       <c r="B75" s="18">
-        <v>46036</v>
+        <v>46051</v>
       </c>
       <c r="C75" s="4">
-        <v>83</v>
+        <v>1</v>
       </c>
       <c r="D75" s="11"/>
       <c r="E75" s="19" t="s">
-        <v>118</v>
+        <v>77</v>
       </c>
       <c r="F75" s="13" t="s">
         <v>90</v>
       </c>
       <c r="G75" s="19">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="H75" s="19">
-        <v>175.4</v>
+        <v>288.05</v>
       </c>
       <c r="I75" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K75" s="6"/>
       <c r="L75" s="4"/>
@@ -3633,23 +3633,23 @@
         <v>1</v>
       </c>
       <c r="B76" s="18">
-        <v>45974</v>
+        <v>46036</v>
       </c>
       <c r="C76" s="4">
-        <v>145</v>
+        <v>83</v>
       </c>
       <c r="D76" s="11"/>
-      <c r="E76" s="20" t="s">
-        <v>46</v>
+      <c r="E76" s="19" t="s">
+        <v>118</v>
       </c>
       <c r="F76" s="13" t="s">
         <v>90</v>
       </c>
       <c r="G76" s="19">
-        <v>1</v>
-      </c>
-      <c r="H76" s="4">
-        <v>2278</v>
+        <v>15</v>
+      </c>
+      <c r="H76" s="19">
+        <v>166.9</v>
       </c>
       <c r="I76" s="4" t="s">
         <v>93</v>
@@ -3667,23 +3667,23 @@
         <v>1</v>
       </c>
       <c r="B77" s="18">
-        <v>46014</v>
+        <v>46036</v>
       </c>
       <c r="C77" s="4">
-        <v>105</v>
+        <v>83</v>
       </c>
       <c r="D77" s="11"/>
       <c r="E77" s="19" t="s">
-        <v>46</v>
+        <v>118</v>
       </c>
       <c r="F77" s="13" t="s">
         <v>90</v>
       </c>
       <c r="G77" s="19">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="H77" s="19">
-        <v>2384</v>
+        <v>175.4</v>
       </c>
       <c r="I77" s="4" t="s">
         <v>93</v>
@@ -3700,14 +3700,14 @@
       <c r="A78" s="14">
         <v>1</v>
       </c>
-      <c r="B78" s="23">
-        <v>46064</v>
+      <c r="B78" s="18">
+        <v>45974</v>
       </c>
       <c r="C78" s="4">
-        <v>55</v>
+        <v>145</v>
       </c>
       <c r="D78" s="11"/>
-      <c r="E78" s="19" t="s">
+      <c r="E78" s="20" t="s">
         <v>46</v>
       </c>
       <c r="F78" s="13" t="s">
@@ -3716,8 +3716,8 @@
       <c r="G78" s="19">
         <v>1</v>
       </c>
-      <c r="H78" s="19">
-        <v>2505.8000000000002</v>
+      <c r="H78" s="4">
+        <v>2278</v>
       </c>
       <c r="I78" s="4" t="s">
         <v>93</v>
@@ -3735,26 +3735,26 @@
         <v>1</v>
       </c>
       <c r="B79" s="18">
-        <v>46092</v>
+        <v>46014</v>
       </c>
       <c r="C79" s="4">
-        <v>27</v>
+        <v>105</v>
       </c>
       <c r="D79" s="11"/>
       <c r="E79" s="19" t="s">
-        <v>129</v>
+        <v>46</v>
       </c>
       <c r="F79" s="13" t="s">
         <v>90</v>
       </c>
       <c r="G79" s="19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H79" s="19">
-        <v>2288.5</v>
+        <v>2384</v>
       </c>
       <c r="I79" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K79" s="6"/>
       <c r="L79" s="4"/>
@@ -3768,24 +3768,24 @@
       <c r="A80" s="14">
         <v>1</v>
       </c>
-      <c r="B80" s="18">
-        <v>46028</v>
+      <c r="B80" s="23">
+        <v>46064</v>
       </c>
       <c r="C80" s="4">
-        <v>91</v>
+        <v>55</v>
       </c>
       <c r="D80" s="11"/>
       <c r="E80" s="19" t="s">
-        <v>110</v>
+        <v>46</v>
       </c>
       <c r="F80" s="13" t="s">
         <v>90</v>
       </c>
       <c r="G80" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H80" s="19">
-        <v>1314.76</v>
+        <v>2505.8000000000002</v>
       </c>
       <c r="I80" s="4" t="s">
         <v>93</v>
@@ -3803,26 +3803,26 @@
         <v>1</v>
       </c>
       <c r="B81" s="18">
-        <v>46014</v>
+        <v>46092</v>
       </c>
       <c r="C81" s="4">
-        <v>105</v>
+        <v>27</v>
       </c>
       <c r="D81" s="11"/>
       <c r="E81" s="19" t="s">
-        <v>86</v>
+        <v>129</v>
       </c>
       <c r="F81" s="13" t="s">
         <v>90</v>
       </c>
       <c r="G81" s="19">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="H81" s="19">
-        <v>167.3</v>
+        <v>2288.5</v>
       </c>
       <c r="I81" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K81" s="6"/>
       <c r="L81" s="4"/>
@@ -3837,26 +3837,26 @@
         <v>1</v>
       </c>
       <c r="B82" s="18">
-        <v>46010</v>
+        <v>46028</v>
       </c>
       <c r="C82" s="4">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="D82" s="11"/>
-      <c r="E82" s="20" t="s">
-        <v>82</v>
+      <c r="E82" s="19" t="s">
+        <v>110</v>
       </c>
       <c r="F82" s="13" t="s">
         <v>90</v>
       </c>
       <c r="G82" s="19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H82" s="19">
-        <v>864</v>
+        <v>1314.76</v>
       </c>
       <c r="I82" s="4" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="K82" s="6"/>
       <c r="L82" s="4"/>
@@ -3871,26 +3871,26 @@
         <v>1</v>
       </c>
       <c r="B83" s="18">
-        <v>46024</v>
+        <v>46014</v>
       </c>
       <c r="C83" s="4">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="D83" s="11"/>
       <c r="E83" s="19" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="F83" s="13" t="s">
         <v>90</v>
       </c>
       <c r="G83" s="19">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="H83" s="19">
-        <v>908</v>
+        <v>167.3</v>
       </c>
       <c r="I83" s="4" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="K83" s="6"/>
       <c r="L83" s="4"/>
@@ -3905,13 +3905,13 @@
         <v>1</v>
       </c>
       <c r="B84" s="18">
-        <v>46028</v>
+        <v>46010</v>
       </c>
       <c r="C84" s="4">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="D84" s="11"/>
-      <c r="E84" s="19" t="s">
+      <c r="E84" s="20" t="s">
         <v>82</v>
       </c>
       <c r="F84" s="13" t="s">
@@ -3921,7 +3921,7 @@
         <v>3</v>
       </c>
       <c r="H84" s="19">
-        <v>952.7</v>
+        <v>864</v>
       </c>
       <c r="I84" s="4" t="s">
         <v>95</v>
@@ -3939,10 +3939,10 @@
         <v>1</v>
       </c>
       <c r="B85" s="18">
-        <v>46050</v>
+        <v>46024</v>
       </c>
       <c r="C85" s="4">
-        <v>1</v>
+        <v>95</v>
       </c>
       <c r="D85" s="11"/>
       <c r="E85" s="19" t="s">
@@ -3952,10 +3952,10 @@
         <v>90</v>
       </c>
       <c r="G85" s="19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H85" s="19">
-        <v>1001.8</v>
+        <v>908</v>
       </c>
       <c r="I85" s="4" t="s">
         <v>95</v>
@@ -3973,26 +3973,26 @@
         <v>1</v>
       </c>
       <c r="B86" s="18">
-        <v>46022</v>
+        <v>46028</v>
       </c>
       <c r="C86" s="4">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="D86" s="11"/>
       <c r="E86" s="19" t="s">
-        <v>99</v>
+        <v>82</v>
       </c>
       <c r="F86" s="13" t="s">
         <v>90</v>
       </c>
       <c r="G86" s="19">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H86" s="19">
-        <v>494.5</v>
+        <v>952.7</v>
       </c>
       <c r="I86" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K86" s="6"/>
       <c r="L86" s="4"/>
@@ -4007,14 +4007,14 @@
         <v>1</v>
       </c>
       <c r="B87" s="18">
-        <v>45973</v>
+        <v>46050</v>
       </c>
       <c r="C87" s="4">
-        <v>146</v>
+        <v>1</v>
       </c>
       <c r="D87" s="11"/>
       <c r="E87" s="19" t="s">
-        <v>40</v>
+        <v>82</v>
       </c>
       <c r="F87" s="13" t="s">
         <v>90</v>
@@ -4023,10 +4023,10 @@
         <v>2</v>
       </c>
       <c r="H87" s="19">
-        <v>1340</v>
+        <v>1001.8</v>
       </c>
       <c r="I87" s="4" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K87" s="6"/>
       <c r="L87" s="4"/>
@@ -4041,26 +4041,26 @@
         <v>1</v>
       </c>
       <c r="B88" s="18">
-        <v>46006</v>
+        <v>46022</v>
       </c>
       <c r="C88" s="4">
-        <v>113</v>
+        <v>97</v>
       </c>
       <c r="D88" s="11"/>
-      <c r="E88" s="20" t="s">
-        <v>40</v>
+      <c r="E88" s="19" t="s">
+        <v>99</v>
       </c>
       <c r="F88" s="13" t="s">
         <v>90</v>
       </c>
       <c r="G88" s="19">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H88" s="19">
-        <v>1408.9</v>
+        <v>494.5</v>
       </c>
       <c r="I88" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K88" s="6"/>
       <c r="L88" s="4"/>
@@ -4075,13 +4075,13 @@
         <v>1</v>
       </c>
       <c r="B89" s="18">
-        <v>46010</v>
+        <v>45973</v>
       </c>
       <c r="C89" s="4">
-        <v>109</v>
+        <v>146</v>
       </c>
       <c r="D89" s="11"/>
-      <c r="E89" s="20" t="s">
+      <c r="E89" s="19" t="s">
         <v>40</v>
       </c>
       <c r="F89" s="13" t="s">
@@ -4091,7 +4091,7 @@
         <v>2</v>
       </c>
       <c r="H89" s="19">
-        <v>1478</v>
+        <v>1340</v>
       </c>
       <c r="I89" s="4" t="s">
         <v>93</v>
@@ -4109,23 +4109,23 @@
         <v>1</v>
       </c>
       <c r="B90" s="18">
-        <v>46008</v>
+        <v>46006</v>
       </c>
       <c r="C90" s="4">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D90" s="11"/>
       <c r="E90" s="20" t="s">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="F90" s="13" t="s">
         <v>90</v>
       </c>
       <c r="G90" s="19">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H90" s="19">
-        <v>431</v>
+        <v>1408.9</v>
       </c>
       <c r="I90" s="4" t="s">
         <v>93</v>
@@ -4143,23 +4143,23 @@
         <v>1</v>
       </c>
       <c r="B91" s="18">
-        <v>46027</v>
+        <v>46010</v>
       </c>
       <c r="C91" s="4">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="D91" s="11"/>
-      <c r="E91" s="19" t="s">
-        <v>80</v>
+      <c r="E91" s="20" t="s">
+        <v>40</v>
       </c>
       <c r="F91" s="13" t="s">
         <v>90</v>
       </c>
       <c r="G91" s="19">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H91" s="19">
-        <v>452.7</v>
+        <v>1478</v>
       </c>
       <c r="I91" s="4" t="s">
         <v>93</v>
@@ -4177,23 +4177,23 @@
         <v>1</v>
       </c>
       <c r="B92" s="18">
-        <v>46036</v>
+        <v>46008</v>
       </c>
       <c r="C92" s="4">
-        <v>83</v>
+        <v>111</v>
       </c>
       <c r="D92" s="11"/>
-      <c r="E92" s="19" t="s">
+      <c r="E92" s="20" t="s">
         <v>80</v>
       </c>
       <c r="F92" s="13" t="s">
         <v>90</v>
       </c>
       <c r="G92" s="19">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H92" s="19">
-        <v>475.66</v>
+        <v>431</v>
       </c>
       <c r="I92" s="4" t="s">
         <v>93</v>
@@ -4211,23 +4211,23 @@
         <v>1</v>
       </c>
       <c r="B93" s="18">
-        <v>45978</v>
+        <v>46027</v>
       </c>
       <c r="C93" s="4">
-        <v>141</v>
+        <v>92</v>
       </c>
       <c r="D93" s="11"/>
-      <c r="E93" s="20" t="s">
-        <v>51</v>
+      <c r="E93" s="19" t="s">
+        <v>80</v>
       </c>
       <c r="F93" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="G93" s="4">
-        <v>2</v>
+      <c r="G93" s="19">
+        <v>5</v>
       </c>
       <c r="H93" s="19">
-        <v>1070</v>
+        <v>452.7</v>
       </c>
       <c r="I93" s="4" t="s">
         <v>93</v>
@@ -4245,23 +4245,23 @@
         <v>1</v>
       </c>
       <c r="B94" s="18">
-        <v>45978</v>
+        <v>46036</v>
       </c>
       <c r="C94" s="4">
-        <v>141</v>
+        <v>83</v>
       </c>
       <c r="D94" s="11"/>
-      <c r="E94" s="20" t="s">
-        <v>51</v>
+      <c r="E94" s="19" t="s">
+        <v>80</v>
       </c>
       <c r="F94" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="G94" s="4">
-        <v>2</v>
-      </c>
-      <c r="H94" s="4">
-        <v>1123.9000000000001</v>
+      <c r="G94" s="19">
+        <v>5</v>
+      </c>
+      <c r="H94" s="19">
+        <v>475.66</v>
       </c>
       <c r="I94" s="4" t="s">
         <v>93</v>
@@ -4279,23 +4279,23 @@
         <v>1</v>
       </c>
       <c r="B95" s="18">
-        <v>45981</v>
+        <v>45978</v>
       </c>
       <c r="C95" s="4">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="D95" s="11"/>
-      <c r="E95" s="19" t="s">
+      <c r="E95" s="20" t="s">
         <v>51</v>
       </c>
       <c r="F95" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="G95" s="19">
+      <c r="G95" s="4">
         <v>2</v>
       </c>
       <c r="H95" s="19">
-        <v>1180</v>
+        <v>1070</v>
       </c>
       <c r="I95" s="4" t="s">
         <v>93</v>
@@ -4313,23 +4313,23 @@
         <v>1</v>
       </c>
       <c r="B96" s="18">
-        <v>45973</v>
+        <v>45978</v>
       </c>
       <c r="C96" s="4">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="D96" s="11"/>
       <c r="E96" s="20" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="F96" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="G96" s="19">
-        <v>8</v>
-      </c>
-      <c r="H96" s="19">
-        <v>320.85000000000002</v>
+      <c r="G96" s="4">
+        <v>2</v>
+      </c>
+      <c r="H96" s="4">
+        <v>1123.9000000000001</v>
       </c>
       <c r="I96" s="4" t="s">
         <v>93</v>
@@ -4353,17 +4353,17 @@
         <v>138</v>
       </c>
       <c r="D97" s="11"/>
-      <c r="E97" s="20" t="s">
-        <v>36</v>
+      <c r="E97" s="19" t="s">
+        <v>51</v>
       </c>
       <c r="F97" s="13" t="s">
         <v>90</v>
       </c>
       <c r="G97" s="19">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H97" s="19">
-        <v>336</v>
+        <v>1180</v>
       </c>
       <c r="I97" s="4" t="s">
         <v>93</v>
@@ -4381,23 +4381,23 @@
         <v>1</v>
       </c>
       <c r="B98" s="18">
-        <v>45972</v>
+        <v>45973</v>
       </c>
       <c r="C98" s="4">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D98" s="11"/>
-      <c r="E98" s="19" t="s">
-        <v>29</v>
+      <c r="E98" s="20" t="s">
+        <v>36</v>
       </c>
       <c r="F98" s="13" t="s">
         <v>90</v>
       </c>
       <c r="G98" s="19">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H98" s="19">
-        <v>434.3</v>
+        <v>320.85000000000002</v>
       </c>
       <c r="I98" s="4" t="s">
         <v>93</v>
@@ -4415,23 +4415,23 @@
         <v>1</v>
       </c>
       <c r="B99" s="18">
-        <v>45978</v>
+        <v>45981</v>
       </c>
       <c r="C99" s="4">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="D99" s="11"/>
       <c r="E99" s="20" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="F99" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="G99" s="4">
-        <v>6</v>
+      <c r="G99" s="19">
+        <v>8</v>
       </c>
       <c r="H99" s="19">
-        <v>456.85</v>
+        <v>336</v>
       </c>
       <c r="I99" s="4" t="s">
         <v>93</v>
@@ -4449,23 +4449,23 @@
         <v>1</v>
       </c>
       <c r="B100" s="18">
-        <v>46069</v>
+        <v>45972</v>
       </c>
       <c r="C100" s="4">
-        <v>50</v>
+        <v>147</v>
       </c>
       <c r="D100" s="11"/>
       <c r="E100" s="19" t="s">
-        <v>123</v>
+        <v>29</v>
       </c>
       <c r="F100" s="13" t="s">
         <v>90</v>
       </c>
       <c r="G100" s="19">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="H100" s="19">
-        <v>149.83000000000001</v>
+        <v>434.3</v>
       </c>
       <c r="I100" s="4" t="s">
         <v>93</v>
@@ -4483,23 +4483,23 @@
         <v>1</v>
       </c>
       <c r="B101" s="18">
-        <v>46015</v>
+        <v>45978</v>
       </c>
       <c r="C101" s="4">
-        <v>104</v>
+        <v>141</v>
       </c>
       <c r="D101" s="11"/>
-      <c r="E101" s="19" t="s">
-        <v>88</v>
+      <c r="E101" s="20" t="s">
+        <v>29</v>
       </c>
       <c r="F101" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="G101" s="19">
-        <v>30</v>
+      <c r="G101" s="4">
+        <v>6</v>
       </c>
       <c r="H101" s="19">
-        <v>80.94</v>
+        <v>456.85</v>
       </c>
       <c r="I101" s="4" t="s">
         <v>93</v>
@@ -4517,23 +4517,23 @@
         <v>1</v>
       </c>
       <c r="B102" s="18">
-        <v>46020</v>
+        <v>46069</v>
       </c>
       <c r="C102" s="4">
-        <v>99</v>
+        <v>50</v>
       </c>
       <c r="D102" s="11"/>
       <c r="E102" s="19" t="s">
-        <v>88</v>
+        <v>123</v>
       </c>
       <c r="F102" s="13" t="s">
         <v>90</v>
       </c>
       <c r="G102" s="19">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="H102" s="19">
-        <v>85</v>
+        <v>149.83000000000001</v>
       </c>
       <c r="I102" s="4" t="s">
         <v>93</v>
@@ -4551,10 +4551,10 @@
         <v>1</v>
       </c>
       <c r="B103" s="18">
-        <v>46021</v>
+        <v>46015</v>
       </c>
       <c r="C103" s="4">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="D103" s="11"/>
       <c r="E103" s="19" t="s">
@@ -4564,10 +4564,10 @@
         <v>90</v>
       </c>
       <c r="G103" s="19">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H103" s="19">
-        <v>89.4</v>
+        <v>80.94</v>
       </c>
       <c r="I103" s="4" t="s">
         <v>93</v>
@@ -4585,10 +4585,10 @@
         <v>1</v>
       </c>
       <c r="B104" s="18">
-        <v>46027</v>
+        <v>46020</v>
       </c>
       <c r="C104" s="4">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="D104" s="11"/>
       <c r="E104" s="19" t="s">
@@ -4598,10 +4598,10 @@
         <v>90</v>
       </c>
       <c r="G104" s="19">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H104" s="19">
-        <v>93.71</v>
+        <v>85</v>
       </c>
       <c r="I104" s="4" t="s">
         <v>93</v>
@@ -4619,26 +4619,26 @@
         <v>1</v>
       </c>
       <c r="B105" s="18">
-        <v>46050</v>
+        <v>46021</v>
       </c>
       <c r="C105" s="4">
-        <v>1</v>
+        <v>98</v>
       </c>
       <c r="D105" s="11"/>
       <c r="E105" s="19" t="s">
-        <v>124</v>
+        <v>88</v>
       </c>
       <c r="F105" s="13" t="s">
         <v>90</v>
       </c>
       <c r="G105" s="19">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="H105" s="19">
-        <v>1098</v>
+        <v>89.4</v>
       </c>
       <c r="I105" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K105" s="6"/>
       <c r="L105" s="4"/>
@@ -4653,26 +4653,26 @@
         <v>1</v>
       </c>
       <c r="B106" s="18">
-        <v>46051</v>
+        <v>46027</v>
       </c>
       <c r="C106" s="4">
-        <v>1</v>
+        <v>92</v>
       </c>
       <c r="D106" s="11"/>
       <c r="E106" s="19" t="s">
-        <v>124</v>
+        <v>88</v>
       </c>
       <c r="F106" s="13" t="s">
         <v>90</v>
       </c>
       <c r="G106" s="19">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="H106" s="19">
-        <v>1152.9000000000001</v>
+        <v>93.71</v>
       </c>
       <c r="I106" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K106" s="6"/>
       <c r="L106" s="4"/>
@@ -4687,10 +4687,10 @@
         <v>1</v>
       </c>
       <c r="B107" s="18">
-        <v>46069</v>
+        <v>46050</v>
       </c>
       <c r="C107" s="4">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="D107" s="11"/>
       <c r="E107" s="19" t="s">
@@ -4703,7 +4703,7 @@
         <v>2</v>
       </c>
       <c r="H107" s="19">
-        <v>1210.5</v>
+        <v>1098</v>
       </c>
       <c r="I107" s="4" t="s">
         <v>94</v>
@@ -4721,14 +4721,14 @@
         <v>1</v>
       </c>
       <c r="B108" s="18">
-        <v>46049</v>
+        <v>46051</v>
       </c>
       <c r="C108" s="4">
         <v>1</v>
       </c>
       <c r="D108" s="11"/>
       <c r="E108" s="19" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F108" s="13" t="s">
         <v>90</v>
@@ -4737,10 +4737,10 @@
         <v>2</v>
       </c>
       <c r="H108" s="19">
-        <v>1224</v>
+        <v>1152.9000000000001</v>
       </c>
       <c r="I108" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K108" s="6"/>
       <c r="L108" s="4"/>
@@ -4755,14 +4755,14 @@
         <v>1</v>
       </c>
       <c r="B109" s="18">
-        <v>45982</v>
+        <v>46069</v>
       </c>
       <c r="C109" s="4">
-        <v>137</v>
+        <v>50</v>
       </c>
       <c r="D109" s="11"/>
-      <c r="E109" s="20" t="s">
-        <v>62</v>
+      <c r="E109" s="19" t="s">
+        <v>124</v>
       </c>
       <c r="F109" s="13" t="s">
         <v>90</v>
@@ -4771,10 +4771,10 @@
         <v>2</v>
       </c>
       <c r="H109" s="19">
-        <v>1469.5</v>
+        <v>1210.5</v>
       </c>
       <c r="I109" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K109" s="6"/>
       <c r="L109" s="4"/>
@@ -4789,14 +4789,14 @@
         <v>1</v>
       </c>
       <c r="B110" s="18">
-        <v>46006</v>
+        <v>46049</v>
       </c>
       <c r="C110" s="4">
-        <v>113</v>
+        <v>1</v>
       </c>
       <c r="D110" s="11"/>
-      <c r="E110" s="20" t="s">
-        <v>62</v>
+      <c r="E110" s="19" t="s">
+        <v>125</v>
       </c>
       <c r="F110" s="13" t="s">
         <v>90</v>
@@ -4805,10 +4805,10 @@
         <v>2</v>
       </c>
       <c r="H110" s="19">
-        <v>1699</v>
+        <v>1224</v>
       </c>
       <c r="I110" s="4" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K110" s="6"/>
       <c r="L110" s="4"/>
@@ -4823,10 +4823,10 @@
         <v>1</v>
       </c>
       <c r="B111" s="18">
-        <v>46007</v>
+        <v>45982</v>
       </c>
       <c r="C111" s="4">
-        <v>112</v>
+        <v>137</v>
       </c>
       <c r="D111" s="11"/>
       <c r="E111" s="20" t="s">
@@ -4839,7 +4839,7 @@
         <v>2</v>
       </c>
       <c r="H111" s="19">
-        <v>1787</v>
+        <v>1469.5</v>
       </c>
       <c r="I111" s="4" t="s">
         <v>93</v>
@@ -4857,10 +4857,10 @@
         <v>1</v>
       </c>
       <c r="B112" s="18">
-        <v>46010</v>
+        <v>46006</v>
       </c>
       <c r="C112" s="4">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="D112" s="11"/>
       <c r="E112" s="20" t="s">
@@ -4873,7 +4873,7 @@
         <v>2</v>
       </c>
       <c r="H112" s="19">
-        <v>1620</v>
+        <v>1699</v>
       </c>
       <c r="I112" s="4" t="s">
         <v>93</v>
@@ -4891,10 +4891,10 @@
         <v>1</v>
       </c>
       <c r="B113" s="18">
-        <v>46013</v>
+        <v>46007</v>
       </c>
       <c r="C113" s="4">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="D113" s="11"/>
       <c r="E113" s="20" t="s">
@@ -4904,10 +4904,10 @@
         <v>90</v>
       </c>
       <c r="G113" s="19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H113" s="19">
-        <v>1897.2</v>
+        <v>1787</v>
       </c>
       <c r="I113" s="4" t="s">
         <v>93</v>
@@ -4925,10 +4925,10 @@
         <v>1</v>
       </c>
       <c r="B114" s="18">
-        <v>46013</v>
+        <v>46010</v>
       </c>
       <c r="C114" s="4">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D114" s="11"/>
       <c r="E114" s="20" t="s">
@@ -4938,10 +4938,10 @@
         <v>90</v>
       </c>
       <c r="G114" s="19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H114" s="19">
-        <v>1959.3</v>
+        <v>1620</v>
       </c>
       <c r="I114" s="4" t="s">
         <v>93</v>
@@ -4959,13 +4959,13 @@
         <v>1</v>
       </c>
       <c r="B115" s="18">
-        <v>46097</v>
+        <v>46013</v>
       </c>
       <c r="C115" s="4">
-        <v>22</v>
+        <v>106</v>
       </c>
       <c r="D115" s="11"/>
-      <c r="E115" s="19" t="s">
+      <c r="E115" s="20" t="s">
         <v>62</v>
       </c>
       <c r="F115" s="13" t="s">
@@ -4975,7 +4975,7 @@
         <v>1</v>
       </c>
       <c r="H115" s="19">
-        <v>1543.5</v>
+        <v>1897.2</v>
       </c>
       <c r="I115" s="4" t="s">
         <v>93</v>
@@ -4993,26 +4993,26 @@
         <v>1</v>
       </c>
       <c r="B116" s="18">
-        <v>46029</v>
+        <v>46013</v>
       </c>
       <c r="C116" s="4">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="D116" s="11"/>
-      <c r="E116" s="19" t="s">
-        <v>113</v>
+      <c r="E116" s="20" t="s">
+        <v>62</v>
       </c>
       <c r="F116" s="13" t="s">
         <v>90</v>
       </c>
       <c r="G116" s="19">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H116" s="19">
-        <v>383</v>
-      </c>
-      <c r="I116" s="4" t="e">
-        <v>#N/A</v>
+        <v>1959.3</v>
+      </c>
+      <c r="I116" s="4" t="s">
+        <v>93</v>
       </c>
       <c r="K116" s="6"/>
       <c r="L116" s="4"/>
@@ -5027,26 +5027,26 @@
         <v>1</v>
       </c>
       <c r="B117" s="18">
-        <v>46092</v>
+        <v>46097</v>
       </c>
       <c r="C117" s="4">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D117" s="11"/>
       <c r="E117" s="19" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="F117" s="13" t="s">
         <v>90</v>
       </c>
       <c r="G117" s="19">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H117" s="19">
-        <v>401.45</v>
-      </c>
-      <c r="I117" s="4" t="e">
-        <v>#N/A</v>
+        <v>1543.5</v>
+      </c>
+      <c r="I117" s="4" t="s">
+        <v>93</v>
       </c>
       <c r="K117" s="6"/>
       <c r="L117" s="4"/>
@@ -5061,10 +5061,10 @@
         <v>1</v>
       </c>
       <c r="B118" s="18">
-        <v>46099</v>
+        <v>46029</v>
       </c>
       <c r="C118" s="4">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="D118" s="11"/>
       <c r="E118" s="19" t="s">
@@ -5077,7 +5077,7 @@
         <v>7</v>
       </c>
       <c r="H118" s="19">
-        <v>422</v>
+        <v>383</v>
       </c>
       <c r="I118" s="4" t="e">
         <v>#N/A</v>
@@ -5095,10 +5095,10 @@
         <v>1</v>
       </c>
       <c r="B119" s="18">
-        <v>46104</v>
+        <v>46092</v>
       </c>
       <c r="C119" s="4">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="D119" s="11"/>
       <c r="E119" s="19" t="s">
@@ -5111,7 +5111,7 @@
         <v>7</v>
       </c>
       <c r="H119" s="19">
-        <v>432.9</v>
+        <v>401.45</v>
       </c>
       <c r="I119" s="4" t="e">
         <v>#N/A</v>
@@ -5129,10 +5129,10 @@
         <v>1</v>
       </c>
       <c r="B120" s="18">
-        <v>46106</v>
+        <v>46099</v>
       </c>
       <c r="C120" s="4">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="D120" s="11"/>
       <c r="E120" s="19" t="s">
@@ -5145,7 +5145,7 @@
         <v>7</v>
       </c>
       <c r="H120" s="19">
-        <v>465</v>
+        <v>422</v>
       </c>
       <c r="I120" s="4" t="e">
         <v>#N/A</v>
@@ -5163,10 +5163,10 @@
         <v>1</v>
       </c>
       <c r="B121" s="18">
-        <v>46118</v>
+        <v>46104</v>
       </c>
       <c r="C121" s="4">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="D121" s="11"/>
       <c r="E121" s="19" t="s">
@@ -5179,7 +5179,7 @@
         <v>7</v>
       </c>
       <c r="H121" s="19">
-        <v>489.56</v>
+        <v>432.9</v>
       </c>
       <c r="I121" s="4" t="e">
         <v>#N/A</v>
@@ -5197,26 +5197,26 @@
         <v>1</v>
       </c>
       <c r="B122" s="18">
-        <v>45953</v>
+        <v>46106</v>
       </c>
       <c r="C122" s="4">
-        <v>166</v>
+        <v>1</v>
       </c>
       <c r="D122" s="11"/>
       <c r="E122" s="19" t="s">
-        <v>14</v>
+        <v>113</v>
       </c>
       <c r="F122" s="13" t="s">
         <v>90</v>
       </c>
       <c r="G122" s="19">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H122" s="19">
-        <v>950</v>
-      </c>
-      <c r="I122" s="4" t="s">
-        <v>94</v>
+        <v>465</v>
+      </c>
+      <c r="I122" s="4" t="e">
+        <v>#N/A</v>
       </c>
       <c r="K122" s="6"/>
       <c r="L122" s="4"/>
@@ -5231,26 +5231,26 @@
         <v>1</v>
       </c>
       <c r="B123" s="18">
-        <v>45971</v>
+        <v>46118</v>
       </c>
       <c r="C123" s="4">
-        <v>148</v>
+        <v>1</v>
       </c>
       <c r="D123" s="11"/>
       <c r="E123" s="19" t="s">
-        <v>14</v>
+        <v>113</v>
       </c>
       <c r="F123" s="13" t="s">
         <v>90</v>
       </c>
       <c r="G123" s="19">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H123" s="19">
-        <v>997.5</v>
-      </c>
-      <c r="I123" s="4" t="s">
-        <v>94</v>
+        <v>489.56</v>
+      </c>
+      <c r="I123" s="4" t="e">
+        <v>#N/A</v>
       </c>
       <c r="K123" s="6"/>
       <c r="L123" s="4"/>
@@ -5265,10 +5265,10 @@
         <v>1</v>
       </c>
       <c r="B124" s="18">
-        <v>46013</v>
+        <v>45953</v>
       </c>
       <c r="C124" s="4">
-        <v>106</v>
+        <v>166</v>
       </c>
       <c r="D124" s="11"/>
       <c r="E124" s="19" t="s">
@@ -5281,7 +5281,7 @@
         <v>2</v>
       </c>
       <c r="H124" s="19">
-        <v>1049.2</v>
+        <v>950</v>
       </c>
       <c r="I124" s="4" t="s">
         <v>94</v>
@@ -5299,10 +5299,10 @@
         <v>1</v>
       </c>
       <c r="B125" s="18">
-        <v>46022</v>
+        <v>45971</v>
       </c>
       <c r="C125" s="4">
-        <v>97</v>
+        <v>148</v>
       </c>
       <c r="D125" s="11"/>
       <c r="E125" s="19" t="s">
@@ -5315,7 +5315,7 @@
         <v>2</v>
       </c>
       <c r="H125" s="19">
-        <v>1101.9000000000001</v>
+        <v>997.5</v>
       </c>
       <c r="I125" s="4" t="s">
         <v>94</v>
@@ -5333,26 +5333,26 @@
         <v>1</v>
       </c>
       <c r="B126" s="18">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="C126" s="4">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D126" s="11"/>
-      <c r="E126" s="20" t="s">
-        <v>83</v>
+      <c r="E126" s="19" t="s">
+        <v>14</v>
       </c>
       <c r="F126" s="13" t="s">
         <v>90</v>
       </c>
       <c r="G126" s="19">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H126" s="19">
-        <v>449</v>
-      </c>
-      <c r="I126" s="4" t="e">
-        <v>#N/A</v>
+        <v>1049.2</v>
+      </c>
+      <c r="I126" s="4" t="s">
+        <v>94</v>
       </c>
       <c r="K126" s="6"/>
       <c r="L126" s="4"/>
@@ -5367,26 +5367,26 @@
         <v>1</v>
       </c>
       <c r="B127" s="18">
-        <v>46010</v>
+        <v>46022</v>
       </c>
       <c r="C127" s="4">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="D127" s="11"/>
-      <c r="E127" s="20" t="s">
-        <v>83</v>
+      <c r="E127" s="19" t="s">
+        <v>14</v>
       </c>
       <c r="F127" s="13" t="s">
         <v>90</v>
       </c>
       <c r="G127" s="19">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H127" s="19">
-        <v>471.2</v>
-      </c>
-      <c r="I127" s="4" t="e">
-        <v>#N/A</v>
+        <v>1101.9000000000001</v>
+      </c>
+      <c r="I127" s="4" t="s">
+        <v>94</v>
       </c>
       <c r="K127" s="6"/>
       <c r="L127" s="4"/>
@@ -5401,13 +5401,13 @@
         <v>1</v>
       </c>
       <c r="B128" s="18">
-        <v>46013</v>
+        <v>46010</v>
       </c>
       <c r="C128" s="4">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D128" s="11"/>
-      <c r="E128" s="19" t="s">
+      <c r="E128" s="20" t="s">
         <v>83</v>
       </c>
       <c r="F128" s="13" t="s">
@@ -5417,7 +5417,7 @@
         <v>5</v>
       </c>
       <c r="H128" s="19">
-        <v>494.65</v>
+        <v>449</v>
       </c>
       <c r="I128" s="4" t="e">
         <v>#N/A</v>
@@ -5435,13 +5435,13 @@
         <v>1</v>
       </c>
       <c r="B129" s="18">
-        <v>46065</v>
+        <v>46010</v>
       </c>
       <c r="C129" s="4">
-        <v>54</v>
+        <v>109</v>
       </c>
       <c r="D129" s="11"/>
-      <c r="E129" s="19" t="s">
+      <c r="E129" s="20" t="s">
         <v>83</v>
       </c>
       <c r="F129" s="13" t="s">
@@ -5451,7 +5451,7 @@
         <v>5</v>
       </c>
       <c r="H129" s="19">
-        <v>521.95000000000005</v>
+        <v>471.2</v>
       </c>
       <c r="I129" s="4" t="e">
         <v>#N/A</v>
@@ -5469,26 +5469,26 @@
         <v>1</v>
       </c>
       <c r="B130" s="18">
-        <v>45986</v>
+        <v>46013</v>
       </c>
       <c r="C130" s="4">
-        <v>133</v>
+        <v>106</v>
       </c>
       <c r="D130" s="11"/>
-      <c r="E130" s="4" t="s">
-        <v>65</v>
+      <c r="E130" s="19" t="s">
+        <v>83</v>
       </c>
       <c r="F130" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="G130" s="4">
-        <v>1</v>
-      </c>
-      <c r="H130" s="4">
-        <v>1910</v>
-      </c>
-      <c r="I130" s="4" t="s">
-        <v>93</v>
+      <c r="G130" s="19">
+        <v>5</v>
+      </c>
+      <c r="H130" s="19">
+        <v>494.65</v>
+      </c>
+      <c r="I130" s="4" t="e">
+        <v>#N/A</v>
       </c>
       <c r="K130" s="6"/>
       <c r="L130" s="4"/>
@@ -5502,27 +5502,27 @@
       <c r="A131" s="14">
         <v>1</v>
       </c>
-      <c r="B131" s="23">
-        <v>46064</v>
+      <c r="B131" s="18">
+        <v>46065</v>
       </c>
       <c r="C131" s="4">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D131" s="11"/>
       <c r="E131" s="19" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="F131" s="13" t="s">
         <v>90</v>
       </c>
       <c r="G131" s="19">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H131" s="19">
-        <v>2006.1</v>
-      </c>
-      <c r="I131" s="4" t="s">
-        <v>93</v>
+        <v>521.95000000000005</v>
+      </c>
+      <c r="I131" s="4" t="e">
+        <v>#N/A</v>
       </c>
       <c r="K131" s="6"/>
       <c r="L131" s="4"/>
@@ -5537,23 +5537,23 @@
         <v>1</v>
       </c>
       <c r="B132" s="18">
-        <v>45978</v>
+        <v>45986</v>
       </c>
       <c r="C132" s="4">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="D132" s="11"/>
-      <c r="E132" s="20" t="s">
-        <v>53</v>
+      <c r="E132" s="4" t="s">
+        <v>65</v>
       </c>
       <c r="F132" s="13" t="s">
         <v>90</v>
       </c>
       <c r="G132" s="4">
-        <v>2</v>
-      </c>
-      <c r="H132" s="19">
-        <v>1468.4</v>
+        <v>1</v>
+      </c>
+      <c r="H132" s="4">
+        <v>1910</v>
       </c>
       <c r="I132" s="4" t="s">
         <v>93</v>
@@ -5570,15 +5570,15 @@
       <c r="A133" s="14">
         <v>1</v>
       </c>
-      <c r="B133" s="18">
-        <v>45992</v>
+      <c r="B133" s="23">
+        <v>46064</v>
       </c>
       <c r="C133" s="4">
-        <v>127</v>
+        <v>55</v>
       </c>
       <c r="D133" s="11"/>
-      <c r="E133" s="20" t="s">
-        <v>53</v>
+      <c r="E133" s="19" t="s">
+        <v>65</v>
       </c>
       <c r="F133" s="13" t="s">
         <v>90</v>
@@ -5587,7 +5587,7 @@
         <v>1</v>
       </c>
       <c r="H133" s="19">
-        <v>1555.7</v>
+        <v>2006.1</v>
       </c>
       <c r="I133" s="4" t="s">
         <v>93</v>
@@ -5605,10 +5605,10 @@
         <v>1</v>
       </c>
       <c r="B134" s="18">
-        <v>46023</v>
+        <v>45978</v>
       </c>
       <c r="C134" s="4">
-        <v>96</v>
+        <v>141</v>
       </c>
       <c r="D134" s="11"/>
       <c r="E134" s="20" t="s">
@@ -5617,11 +5617,11 @@
       <c r="F134" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="G134" s="19">
-        <v>1</v>
+      <c r="G134" s="4">
+        <v>2</v>
       </c>
       <c r="H134" s="19">
-        <v>1633</v>
+        <v>1468.4</v>
       </c>
       <c r="I134" s="4" t="s">
         <v>93</v>
@@ -5638,14 +5638,14 @@
       <c r="A135" s="14">
         <v>1</v>
       </c>
-      <c r="B135" s="23">
-        <v>46064</v>
+      <c r="B135" s="18">
+        <v>45992</v>
       </c>
       <c r="C135" s="4">
-        <v>55</v>
+        <v>127</v>
       </c>
       <c r="D135" s="11"/>
-      <c r="E135" s="19" t="s">
+      <c r="E135" s="20" t="s">
         <v>53</v>
       </c>
       <c r="F135" s="13" t="s">
@@ -5655,7 +5655,7 @@
         <v>1</v>
       </c>
       <c r="H135" s="19">
-        <v>1715</v>
+        <v>1555.7</v>
       </c>
       <c r="I135" s="4" t="s">
         <v>93</v>
@@ -5673,13 +5673,13 @@
         <v>1</v>
       </c>
       <c r="B136" s="18">
-        <v>46080</v>
+        <v>46023</v>
       </c>
       <c r="C136" s="4">
-        <v>39</v>
+        <v>96</v>
       </c>
       <c r="D136" s="11"/>
-      <c r="E136" s="19" t="s">
+      <c r="E136" s="20" t="s">
         <v>53</v>
       </c>
       <c r="F136" s="13" t="s">
@@ -5689,7 +5689,7 @@
         <v>1</v>
       </c>
       <c r="H136" s="19">
-        <v>1801</v>
+        <v>1633</v>
       </c>
       <c r="I136" s="4" t="s">
         <v>93</v>
@@ -5706,27 +5706,27 @@
       <c r="A137" s="14">
         <v>1</v>
       </c>
-      <c r="B137" s="18">
-        <v>45985</v>
+      <c r="B137" s="23">
+        <v>46064</v>
       </c>
       <c r="C137" s="4">
-        <v>134</v>
+        <v>55</v>
       </c>
       <c r="D137" s="11"/>
       <c r="E137" s="19" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="F137" s="13" t="s">
         <v>90</v>
       </c>
       <c r="G137" s="19">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H137" s="19">
-        <v>354.45</v>
+        <v>1715</v>
       </c>
       <c r="I137" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K137" s="6"/>
       <c r="L137" s="4"/>
@@ -5741,26 +5741,26 @@
         <v>1</v>
       </c>
       <c r="B138" s="18">
-        <v>45989</v>
+        <v>46080</v>
       </c>
       <c r="C138" s="4">
-        <v>130</v>
+        <v>39</v>
       </c>
       <c r="D138" s="11"/>
       <c r="E138" s="19" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="F138" s="13" t="s">
         <v>90</v>
       </c>
       <c r="G138" s="19">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H138" s="19">
-        <v>372</v>
+        <v>1801</v>
       </c>
       <c r="I138" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K138" s="6"/>
       <c r="L138" s="4"/>
@@ -5775,23 +5775,23 @@
         <v>1</v>
       </c>
       <c r="B139" s="18">
-        <v>46013</v>
+        <v>45985</v>
       </c>
       <c r="C139" s="4">
-        <v>106</v>
+        <v>134</v>
       </c>
       <c r="D139" s="11"/>
-      <c r="E139" s="20" t="s">
+      <c r="E139" s="19" t="s">
         <v>63</v>
       </c>
       <c r="F139" s="13" t="s">
         <v>90</v>
       </c>
       <c r="G139" s="19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H139" s="19">
-        <v>390.7</v>
+        <v>354.45</v>
       </c>
       <c r="I139" s="4" t="s">
         <v>94</v>
@@ -5809,26 +5809,26 @@
         <v>1</v>
       </c>
       <c r="B140" s="18">
-        <v>46015</v>
+        <v>45989</v>
       </c>
       <c r="C140" s="4">
-        <v>104</v>
+        <v>130</v>
       </c>
       <c r="D140" s="11"/>
-      <c r="E140" s="20" t="s">
-        <v>87</v>
+      <c r="E140" s="19" t="s">
+        <v>63</v>
       </c>
       <c r="F140" s="13" t="s">
         <v>90</v>
       </c>
       <c r="G140" s="19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H140" s="19">
-        <v>298</v>
+        <v>372</v>
       </c>
       <c r="I140" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K140" s="6"/>
       <c r="L140" s="4"/>
@@ -5843,26 +5843,26 @@
         <v>1</v>
       </c>
       <c r="B141" s="18">
-        <v>46015</v>
+        <v>46013</v>
       </c>
       <c r="C141" s="4">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D141" s="11"/>
       <c r="E141" s="20" t="s">
-        <v>87</v>
+        <v>63</v>
       </c>
       <c r="F141" s="13" t="s">
         <v>90</v>
       </c>
       <c r="G141" s="19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H141" s="19">
-        <v>312.89999999999998</v>
+        <v>390.7</v>
       </c>
       <c r="I141" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K141" s="6"/>
       <c r="L141" s="4"/>
@@ -5877,26 +5877,26 @@
         <v>1</v>
       </c>
       <c r="B142" s="18">
-        <v>46027</v>
+        <v>46015</v>
       </c>
       <c r="C142" s="4">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="D142" s="11"/>
-      <c r="E142" s="19" t="s">
-        <v>106</v>
+      <c r="E142" s="20" t="s">
+        <v>87</v>
       </c>
       <c r="F142" s="13" t="s">
         <v>90</v>
       </c>
       <c r="G142" s="19">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H142" s="19">
-        <v>760.99</v>
+        <v>298</v>
       </c>
       <c r="I142" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K142" s="6"/>
       <c r="L142" s="4"/>
@@ -5911,26 +5911,26 @@
         <v>1</v>
       </c>
       <c r="B143" s="18">
-        <v>46071</v>
+        <v>46015</v>
       </c>
       <c r="C143" s="4">
-        <v>48</v>
+        <v>104</v>
       </c>
       <c r="D143" s="11"/>
-      <c r="E143" s="19" t="s">
-        <v>106</v>
+      <c r="E143" s="20" t="s">
+        <v>87</v>
       </c>
       <c r="F143" s="13" t="s">
         <v>90</v>
       </c>
       <c r="G143" s="19">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H143" s="19">
-        <v>795.8</v>
+        <v>312.89999999999998</v>
       </c>
       <c r="I143" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K143" s="6"/>
       <c r="L143" s="4"/>
@@ -5945,23 +5945,23 @@
         <v>1</v>
       </c>
       <c r="B144" s="18">
-        <v>46029</v>
+        <v>46027</v>
       </c>
       <c r="C144" s="4">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D144" s="11"/>
-      <c r="E144" s="20" t="s">
-        <v>111</v>
+      <c r="E144" s="19" t="s">
+        <v>106</v>
       </c>
       <c r="F144" s="13" t="s">
         <v>90</v>
       </c>
       <c r="G144" s="19">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H144" s="19">
-        <v>1751.9</v>
+        <v>760.99</v>
       </c>
       <c r="I144" s="4" t="s">
         <v>94</v>
@@ -5979,23 +5979,23 @@
         <v>1</v>
       </c>
       <c r="B145" s="18">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="C145" s="4">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D145" s="11"/>
       <c r="E145" s="19" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="F145" s="13" t="s">
         <v>90</v>
       </c>
       <c r="G145" s="19">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H145" s="19">
-        <v>1838.9</v>
+        <v>795.8</v>
       </c>
       <c r="I145" s="4" t="s">
         <v>94</v>
@@ -6013,23 +6013,23 @@
         <v>1</v>
       </c>
       <c r="B146" s="18">
-        <v>45999</v>
+        <v>46029</v>
       </c>
       <c r="C146" s="4">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="D146" s="11"/>
-      <c r="E146" s="19" t="s">
-        <v>73</v>
+      <c r="E146" s="20" t="s">
+        <v>111</v>
       </c>
       <c r="F146" s="13" t="s">
         <v>90</v>
       </c>
       <c r="G146" s="19">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H146" s="19">
-        <v>273</v>
+        <v>1751.9</v>
       </c>
       <c r="I146" s="4" t="s">
         <v>94</v>
@@ -6047,23 +6047,23 @@
         <v>1</v>
       </c>
       <c r="B147" s="18">
-        <v>46013</v>
+        <v>46069</v>
       </c>
       <c r="C147" s="4">
-        <v>106</v>
+        <v>50</v>
       </c>
       <c r="D147" s="11"/>
       <c r="E147" s="19" t="s">
-        <v>73</v>
+        <v>111</v>
       </c>
       <c r="F147" s="13" t="s">
         <v>90</v>
       </c>
       <c r="G147" s="19">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H147" s="19">
-        <v>285.60000000000002</v>
+        <v>1838.9</v>
       </c>
       <c r="I147" s="4" t="s">
         <v>94</v>
@@ -6081,10 +6081,10 @@
         <v>1</v>
       </c>
       <c r="B148" s="18">
-        <v>46020</v>
+        <v>45999</v>
       </c>
       <c r="C148" s="4">
-        <v>99</v>
+        <v>120</v>
       </c>
       <c r="D148" s="11"/>
       <c r="E148" s="19" t="s">
@@ -6094,10 +6094,10 @@
         <v>90</v>
       </c>
       <c r="G148" s="19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H148" s="19">
-        <v>300</v>
+        <v>273</v>
       </c>
       <c r="I148" s="4" t="s">
         <v>94</v>
@@ -6115,10 +6115,10 @@
         <v>1</v>
       </c>
       <c r="B149" s="18">
-        <v>46021</v>
+        <v>46013</v>
       </c>
       <c r="C149" s="4">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="D149" s="11"/>
       <c r="E149" s="19" t="s">
@@ -6128,10 +6128,10 @@
         <v>90</v>
       </c>
       <c r="G149" s="19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H149" s="19">
-        <v>314.8</v>
+        <v>285.60000000000002</v>
       </c>
       <c r="I149" s="4" t="s">
         <v>94</v>
@@ -6149,10 +6149,10 @@
         <v>1</v>
       </c>
       <c r="B150" s="18">
-        <v>46024</v>
+        <v>46020</v>
       </c>
       <c r="C150" s="4">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D150" s="11"/>
       <c r="E150" s="19" t="s">
@@ -6165,7 +6165,7 @@
         <v>8</v>
       </c>
       <c r="H150" s="19">
-        <v>330.9</v>
+        <v>300</v>
       </c>
       <c r="I150" s="4" t="s">
         <v>94</v>
@@ -6183,10 +6183,10 @@
         <v>1</v>
       </c>
       <c r="B151" s="18">
-        <v>46028</v>
+        <v>46021</v>
       </c>
       <c r="C151" s="4">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="D151" s="11"/>
       <c r="E151" s="19" t="s">
@@ -6199,7 +6199,7 @@
         <v>8</v>
       </c>
       <c r="H151" s="19">
-        <v>347.25</v>
+        <v>314.8</v>
       </c>
       <c r="I151" s="4" t="s">
         <v>94</v>
@@ -6217,10 +6217,10 @@
         <v>1</v>
       </c>
       <c r="B152" s="18">
-        <v>46036</v>
+        <v>46024</v>
       </c>
       <c r="C152" s="4">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="D152" s="11"/>
       <c r="E152" s="19" t="s">
@@ -6233,7 +6233,7 @@
         <v>8</v>
       </c>
       <c r="H152" s="19">
-        <v>364.4</v>
+        <v>330.9</v>
       </c>
       <c r="I152" s="4" t="s">
         <v>94</v>
@@ -6251,10 +6251,10 @@
         <v>1</v>
       </c>
       <c r="B153" s="18">
-        <v>46049</v>
+        <v>46028</v>
       </c>
       <c r="C153" s="4">
-        <v>1</v>
+        <v>91</v>
       </c>
       <c r="D153" s="11"/>
       <c r="E153" s="19" t="s">
@@ -6264,10 +6264,10 @@
         <v>90</v>
       </c>
       <c r="G153" s="19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H153" s="19">
-        <v>383</v>
+        <v>347.25</v>
       </c>
       <c r="I153" s="4" t="s">
         <v>94</v>
@@ -6285,10 +6285,10 @@
         <v>1</v>
       </c>
       <c r="B154" s="18">
-        <v>46050</v>
+        <v>46036</v>
       </c>
       <c r="C154" s="4">
-        <v>1</v>
+        <v>83</v>
       </c>
       <c r="D154" s="11"/>
       <c r="E154" s="19" t="s">
@@ -6298,10 +6298,10 @@
         <v>90</v>
       </c>
       <c r="G154" s="19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H154" s="19">
-        <v>402.2</v>
+        <v>364.4</v>
       </c>
       <c r="I154" s="4" t="s">
         <v>94</v>
@@ -6319,7 +6319,7 @@
         <v>1</v>
       </c>
       <c r="B155" s="18">
-        <v>46051</v>
+        <v>46049</v>
       </c>
       <c r="C155" s="4">
         <v>1</v>
@@ -6335,7 +6335,7 @@
         <v>7</v>
       </c>
       <c r="H155" s="19">
-        <v>422.3</v>
+        <v>383</v>
       </c>
       <c r="I155" s="4" t="s">
         <v>94</v>
@@ -6353,26 +6353,26 @@
         <v>1</v>
       </c>
       <c r="B156" s="18">
-        <v>46001</v>
+        <v>46050</v>
       </c>
       <c r="C156" s="4">
-        <v>118</v>
+        <v>1</v>
       </c>
       <c r="D156" s="11"/>
       <c r="E156" s="19" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="F156" s="13" t="s">
         <v>90</v>
       </c>
       <c r="G156" s="19">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="H156" s="19">
-        <v>203.74</v>
+        <v>402.2</v>
       </c>
       <c r="I156" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K156" s="6"/>
       <c r="L156" s="4"/>
@@ -6387,26 +6387,26 @@
         <v>1</v>
       </c>
       <c r="B157" s="18">
-        <v>46028</v>
+        <v>46051</v>
       </c>
       <c r="C157" s="4">
-        <v>91</v>
+        <v>1</v>
       </c>
       <c r="D157" s="11"/>
       <c r="E157" s="19" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="F157" s="13" t="s">
         <v>90</v>
       </c>
       <c r="G157" s="19">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H157" s="19">
-        <v>246.14</v>
+        <v>422.3</v>
       </c>
       <c r="I157" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K157" s="6"/>
       <c r="L157" s="4"/>
@@ -6421,10 +6421,10 @@
         <v>1</v>
       </c>
       <c r="B158" s="18">
-        <v>46034</v>
+        <v>46001</v>
       </c>
       <c r="C158" s="4">
-        <v>85</v>
+        <v>118</v>
       </c>
       <c r="D158" s="11"/>
       <c r="E158" s="19" t="s">
@@ -6434,10 +6434,10 @@
         <v>90</v>
       </c>
       <c r="G158" s="19">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H158" s="19">
-        <v>231.88</v>
+        <v>203.74</v>
       </c>
       <c r="I158" s="4" t="s">
         <v>93</v>
@@ -6455,10 +6455,10 @@
         <v>1</v>
       </c>
       <c r="B159" s="18">
-        <v>46056</v>
+        <v>46028</v>
       </c>
       <c r="C159" s="4">
-        <v>63</v>
+        <v>91</v>
       </c>
       <c r="D159" s="11"/>
       <c r="E159" s="19" t="s">
@@ -6471,7 +6471,7 @@
         <v>10</v>
       </c>
       <c r="H159" s="19">
-        <v>243.5</v>
+        <v>246.14</v>
       </c>
       <c r="I159" s="4" t="s">
         <v>93</v>
@@ -6489,10 +6489,10 @@
         <v>1</v>
       </c>
       <c r="B160" s="18">
-        <v>46056</v>
+        <v>46034</v>
       </c>
       <c r="C160" s="4">
-        <v>63</v>
+        <v>85</v>
       </c>
       <c r="D160" s="11"/>
       <c r="E160" s="19" t="s">
@@ -6502,10 +6502,10 @@
         <v>90</v>
       </c>
       <c r="G160" s="19">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H160" s="19">
-        <v>255.67</v>
+        <v>231.88</v>
       </c>
       <c r="I160" s="4" t="s">
         <v>93</v>
@@ -6539,7 +6539,7 @@
         <v>10</v>
       </c>
       <c r="H161" s="19">
-        <v>268.5</v>
+        <v>243.5</v>
       </c>
       <c r="I161" s="4" t="s">
         <v>93</v>
@@ -6557,13 +6557,13 @@
         <v>1</v>
       </c>
       <c r="B162" s="18">
-        <v>46062</v>
+        <v>46056</v>
       </c>
       <c r="C162" s="4">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D162" s="4"/>
-      <c r="E162" s="20" t="s">
+      <c r="E162" s="19" t="s">
         <v>76</v>
       </c>
       <c r="F162" s="13" t="s">
@@ -6573,7 +6573,7 @@
         <v>10</v>
       </c>
       <c r="H162" s="19">
-        <v>287</v>
+        <v>255.67</v>
       </c>
       <c r="I162" s="4" t="s">
         <v>93</v>
@@ -6591,10 +6591,10 @@
         <v>1</v>
       </c>
       <c r="B163" s="18">
-        <v>46104</v>
+        <v>46056</v>
       </c>
       <c r="C163" s="4">
-        <v>1</v>
+        <v>63</v>
       </c>
       <c r="D163" s="4"/>
       <c r="E163" s="19" t="s">
@@ -6607,7 +6607,7 @@
         <v>10</v>
       </c>
       <c r="H163" s="19">
-        <v>301.2</v>
+        <v>268.5</v>
       </c>
       <c r="I163" s="4" t="s">
         <v>93</v>
@@ -6625,13 +6625,13 @@
         <v>1</v>
       </c>
       <c r="B164" s="18">
-        <v>46106</v>
+        <v>46062</v>
       </c>
       <c r="C164" s="4">
-        <v>1</v>
+        <v>57</v>
       </c>
       <c r="D164" s="4"/>
-      <c r="E164" s="19" t="s">
+      <c r="E164" s="20" t="s">
         <v>76</v>
       </c>
       <c r="F164" s="13" t="s">
@@ -6641,7 +6641,7 @@
         <v>10</v>
       </c>
       <c r="H164" s="19">
-        <v>316.45</v>
+        <v>287</v>
       </c>
       <c r="I164" s="4" t="s">
         <v>93</v>
@@ -6659,7 +6659,7 @@
         <v>1</v>
       </c>
       <c r="B165" s="18">
-        <v>46111</v>
+        <v>46104</v>
       </c>
       <c r="C165" s="4">
         <v>1</v>
@@ -6675,7 +6675,7 @@
         <v>10</v>
       </c>
       <c r="H165" s="19">
-        <v>332.3</v>
+        <v>301.2</v>
       </c>
       <c r="I165" s="4" t="s">
         <v>93</v>
@@ -6693,7 +6693,7 @@
         <v>1</v>
       </c>
       <c r="B166" s="18">
-        <v>46118</v>
+        <v>46106</v>
       </c>
       <c r="C166" s="4">
         <v>1</v>
@@ -6709,7 +6709,7 @@
         <v>10</v>
       </c>
       <c r="H166" s="19">
-        <v>355.95</v>
+        <v>316.45</v>
       </c>
       <c r="I166" s="4" t="s">
         <v>93</v>
@@ -6721,23 +6721,23 @@
         <v>1</v>
       </c>
       <c r="B167" s="18">
-        <v>45974</v>
+        <v>46111</v>
       </c>
       <c r="C167" s="4">
-        <v>145</v>
+        <v>1</v>
       </c>
       <c r="D167" s="4"/>
-      <c r="E167" s="20" t="s">
-        <v>43</v>
+      <c r="E167" s="19" t="s">
+        <v>76</v>
       </c>
       <c r="F167" s="13" t="s">
         <v>90</v>
       </c>
       <c r="G167" s="19">
-        <v>1</v>
-      </c>
-      <c r="H167" s="4">
-        <v>1804.9</v>
+        <v>10</v>
+      </c>
+      <c r="H167" s="19">
+        <v>332.3</v>
       </c>
       <c r="I167" s="4" t="s">
         <v>93</v>
@@ -6749,23 +6749,23 @@
         <v>1</v>
       </c>
       <c r="B168" s="18">
-        <v>45974</v>
+        <v>46118</v>
       </c>
       <c r="C168" s="4">
-        <v>145</v>
+        <v>1</v>
       </c>
       <c r="D168" s="4"/>
-      <c r="E168" s="20" t="s">
-        <v>43</v>
+      <c r="E168" s="19" t="s">
+        <v>76</v>
       </c>
       <c r="F168" s="13" t="s">
         <v>90</v>
       </c>
       <c r="G168" s="19">
-        <v>1</v>
-      </c>
-      <c r="H168" s="4">
-        <v>1895</v>
+        <v>10</v>
+      </c>
+      <c r="H168" s="19">
+        <v>355.95</v>
       </c>
       <c r="I168" s="4" t="s">
         <v>93</v>
@@ -6793,7 +6793,7 @@
         <v>1</v>
       </c>
       <c r="H169" s="4">
-        <v>1979.3</v>
+        <v>1804.9</v>
       </c>
       <c r="I169" s="4" t="s">
         <v>93</v>
@@ -6821,7 +6821,7 @@
         <v>1</v>
       </c>
       <c r="H170" s="4">
-        <v>1720</v>
+        <v>1895</v>
       </c>
       <c r="I170" s="4" t="s">
         <v>93</v>
@@ -6833,26 +6833,26 @@
         <v>1</v>
       </c>
       <c r="B171" s="18">
-        <v>45972</v>
+        <v>45974</v>
       </c>
       <c r="C171" s="4">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D171" s="4"/>
-      <c r="E171" s="19" t="s">
-        <v>30</v>
+      <c r="E171" s="20" t="s">
+        <v>43</v>
       </c>
       <c r="F171" s="13" t="s">
         <v>90</v>
       </c>
       <c r="G171" s="19">
-        <v>2</v>
-      </c>
-      <c r="H171" s="19">
-        <v>1458.5</v>
-      </c>
-      <c r="I171" s="4" t="e">
-        <v>#N/A</v>
+        <v>1</v>
+      </c>
+      <c r="H171" s="4">
+        <v>1979.3</v>
+      </c>
+      <c r="I171" s="4" t="s">
+        <v>93</v>
       </c>
       <c r="J171" s="5"/>
     </row>
@@ -6861,14 +6861,14 @@
         <v>1</v>
       </c>
       <c r="B172" s="18">
-        <v>45985</v>
+        <v>45974</v>
       </c>
       <c r="C172" s="4">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="D172" s="4"/>
-      <c r="E172" s="19" t="s">
-        <v>30</v>
+      <c r="E172" s="20" t="s">
+        <v>43</v>
       </c>
       <c r="F172" s="13" t="s">
         <v>90</v>
@@ -6876,11 +6876,11 @@
       <c r="G172" s="19">
         <v>1</v>
       </c>
-      <c r="H172" s="19">
-        <v>1610</v>
-      </c>
-      <c r="I172" s="4" t="e">
-        <v>#N/A</v>
+      <c r="H172" s="4">
+        <v>1720</v>
+      </c>
+      <c r="I172" s="4" t="s">
+        <v>93</v>
       </c>
       <c r="J172" s="5"/>
     </row>
@@ -6889,23 +6889,23 @@
         <v>1</v>
       </c>
       <c r="B173" s="18">
-        <v>45986</v>
+        <v>45972</v>
       </c>
       <c r="C173" s="4">
-        <v>133</v>
+        <v>147</v>
       </c>
       <c r="D173" s="10"/>
-      <c r="E173" s="4" t="s">
+      <c r="E173" s="19" t="s">
         <v>30</v>
       </c>
       <c r="F173" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="G173" s="4">
-        <v>1</v>
-      </c>
-      <c r="H173" s="4">
-        <v>1535</v>
+      <c r="G173" s="19">
+        <v>2</v>
+      </c>
+      <c r="H173" s="19">
+        <v>1458.5</v>
       </c>
       <c r="I173" s="4" t="e">
         <v>#N/A</v>
@@ -6916,10 +6916,10 @@
         <v>1</v>
       </c>
       <c r="B174" s="18">
-        <v>46013</v>
+        <v>45985</v>
       </c>
       <c r="C174" s="4">
-        <v>106</v>
+        <v>134</v>
       </c>
       <c r="D174" s="10"/>
       <c r="E174" s="19" t="s">
@@ -6932,7 +6932,7 @@
         <v>1</v>
       </c>
       <c r="H174" s="19">
-        <v>1692</v>
+        <v>1610</v>
       </c>
       <c r="I174" s="4" t="e">
         <v>#N/A</v>
@@ -6943,23 +6943,23 @@
         <v>1</v>
       </c>
       <c r="B175" s="18">
-        <v>46027</v>
+        <v>45986</v>
       </c>
       <c r="C175" s="4">
-        <v>92</v>
+        <v>133</v>
       </c>
       <c r="D175" s="10"/>
-      <c r="E175" s="19" t="s">
+      <c r="E175" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F175" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="G175" s="19">
-        <v>1</v>
-      </c>
-      <c r="H175" s="19">
-        <v>1774</v>
+      <c r="G175" s="4">
+        <v>1</v>
+      </c>
+      <c r="H175" s="4">
+        <v>1535</v>
       </c>
       <c r="I175" s="4" t="e">
         <v>#N/A</v>
@@ -6970,10 +6970,10 @@
         <v>1</v>
       </c>
       <c r="B176" s="18">
-        <v>46029</v>
+        <v>46013</v>
       </c>
       <c r="C176" s="4">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="D176" s="10"/>
       <c r="E176" s="19" t="s">
@@ -6986,7 +6986,7 @@
         <v>1</v>
       </c>
       <c r="H176" s="19">
-        <v>1863.9</v>
+        <v>1692</v>
       </c>
       <c r="I176" s="4" t="e">
         <v>#N/A</v>
@@ -6997,26 +6997,26 @@
         <v>1</v>
       </c>
       <c r="B177" s="18">
-        <v>45973</v>
+        <v>46027</v>
       </c>
       <c r="C177" s="4">
-        <v>146</v>
+        <v>92</v>
       </c>
       <c r="D177" s="10"/>
       <c r="E177" s="19" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="F177" s="13" t="s">
         <v>90</v>
       </c>
       <c r="G177" s="19">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H177" s="19">
-        <v>238</v>
-      </c>
-      <c r="I177" s="4" t="s">
-        <v>93</v>
+        <v>1774</v>
+      </c>
+      <c r="I177" s="4" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="178" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -7024,26 +7024,26 @@
         <v>1</v>
       </c>
       <c r="B178" s="18">
-        <v>45974</v>
+        <v>46029</v>
       </c>
       <c r="C178" s="4">
-        <v>145</v>
+        <v>90</v>
       </c>
       <c r="D178" s="10"/>
-      <c r="E178" s="20" t="s">
-        <v>37</v>
+      <c r="E178" s="19" t="s">
+        <v>30</v>
       </c>
       <c r="F178" s="13" t="s">
         <v>90</v>
       </c>
       <c r="G178" s="19">
-        <v>10</v>
-      </c>
-      <c r="H178" s="4">
-        <v>250</v>
-      </c>
-      <c r="I178" s="4" t="s">
-        <v>93</v>
+        <v>1</v>
+      </c>
+      <c r="H178" s="19">
+        <v>1863.9</v>
+      </c>
+      <c r="I178" s="4" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="179" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -7051,13 +7051,13 @@
         <v>1</v>
       </c>
       <c r="B179" s="18">
-        <v>45974</v>
+        <v>45973</v>
       </c>
       <c r="C179" s="4">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D179" s="10"/>
-      <c r="E179" s="20" t="s">
+      <c r="E179" s="19" t="s">
         <v>37</v>
       </c>
       <c r="F179" s="13" t="s">
@@ -7066,8 +7066,8 @@
       <c r="G179" s="19">
         <v>10</v>
       </c>
-      <c r="H179" s="4">
-        <v>262</v>
+      <c r="H179" s="19">
+        <v>238</v>
       </c>
       <c r="I179" s="4" t="s">
         <v>93</v>
@@ -7094,7 +7094,7 @@
         <v>10</v>
       </c>
       <c r="H180" s="4">
-        <v>274.8</v>
+        <v>250</v>
       </c>
       <c r="I180" s="4" t="s">
         <v>93</v>
@@ -7105,23 +7105,23 @@
         <v>1</v>
       </c>
       <c r="B181" s="18">
-        <v>46065</v>
+        <v>45974</v>
       </c>
       <c r="C181" s="4">
-        <v>54</v>
+        <v>145</v>
       </c>
       <c r="D181" s="10"/>
-      <c r="E181" s="19" t="s">
+      <c r="E181" s="20" t="s">
         <v>37</v>
       </c>
       <c r="F181" s="13" t="s">
         <v>90</v>
       </c>
       <c r="G181" s="19">
-        <v>18</v>
-      </c>
-      <c r="H181" s="19">
-        <v>277.68</v>
+        <v>10</v>
+      </c>
+      <c r="H181" s="4">
+        <v>262</v>
       </c>
       <c r="I181" s="4" t="s">
         <v>93</v>
@@ -7132,13 +7132,13 @@
         <v>1</v>
       </c>
       <c r="B182" s="18">
-        <v>46069</v>
+        <v>45974</v>
       </c>
       <c r="C182" s="4">
-        <v>50</v>
+        <v>145</v>
       </c>
       <c r="D182" s="10"/>
-      <c r="E182" s="19" t="s">
+      <c r="E182" s="20" t="s">
         <v>37</v>
       </c>
       <c r="F182" s="13" t="s">
@@ -7147,8 +7147,8 @@
       <c r="G182" s="19">
         <v>10</v>
       </c>
-      <c r="H182" s="19">
-        <v>290</v>
+      <c r="H182" s="4">
+        <v>274.8</v>
       </c>
       <c r="I182" s="4" t="s">
         <v>93</v>
@@ -7159,10 +7159,10 @@
         <v>1</v>
       </c>
       <c r="B183" s="18">
-        <v>46069</v>
+        <v>46065</v>
       </c>
       <c r="C183" s="4">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D183" s="10"/>
       <c r="E183" s="19" t="s">
@@ -7172,10 +7172,10 @@
         <v>90</v>
       </c>
       <c r="G183" s="19">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="H183" s="19">
-        <v>304</v>
+        <v>277.68</v>
       </c>
       <c r="I183" s="4" t="s">
         <v>93</v>
@@ -7186,10 +7186,10 @@
         <v>1</v>
       </c>
       <c r="B184" s="18">
-        <v>46080</v>
+        <v>46069</v>
       </c>
       <c r="C184" s="4">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="D184" s="10"/>
       <c r="E184" s="19" t="s">
@@ -7202,7 +7202,7 @@
         <v>10</v>
       </c>
       <c r="H184" s="19">
-        <v>319.18</v>
+        <v>290</v>
       </c>
       <c r="I184" s="4" t="s">
         <v>93</v>
@@ -7213,10 +7213,10 @@
         <v>1</v>
       </c>
       <c r="B185" s="18">
-        <v>46086</v>
+        <v>46069</v>
       </c>
       <c r="C185" s="4">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="D185" s="10"/>
       <c r="E185" s="19" t="s">
@@ -7229,7 +7229,7 @@
         <v>10</v>
       </c>
       <c r="H185" s="19">
-        <v>335</v>
+        <v>304</v>
       </c>
       <c r="I185" s="4" t="s">
         <v>93</v>
@@ -7240,23 +7240,23 @@
         <v>1</v>
       </c>
       <c r="B186" s="18">
-        <v>45978</v>
+        <v>46080</v>
       </c>
       <c r="C186" s="4">
-        <v>141</v>
+        <v>39</v>
       </c>
       <c r="D186" s="10"/>
-      <c r="E186" s="20" t="s">
-        <v>50</v>
+      <c r="E186" s="19" t="s">
+        <v>37</v>
       </c>
       <c r="F186" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="G186" s="4">
-        <v>4</v>
+      <c r="G186" s="19">
+        <v>10</v>
       </c>
       <c r="H186" s="19">
-        <v>613.04999999999995</v>
+        <v>319.18</v>
       </c>
       <c r="I186" s="4" t="s">
         <v>93</v>
@@ -7267,23 +7267,23 @@
         <v>1</v>
       </c>
       <c r="B187" s="18">
-        <v>45980</v>
+        <v>46086</v>
       </c>
       <c r="C187" s="4">
-        <v>139</v>
+        <v>33</v>
       </c>
       <c r="D187" s="10"/>
-      <c r="E187" s="20" t="s">
-        <v>50</v>
+      <c r="E187" s="19" t="s">
+        <v>37</v>
       </c>
       <c r="F187" s="13" t="s">
         <v>90</v>
       </c>
       <c r="G187" s="19">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H187" s="19">
-        <v>645</v>
+        <v>335</v>
       </c>
       <c r="I187" s="4" t="s">
         <v>93</v>
@@ -7294,23 +7294,23 @@
         <v>1</v>
       </c>
       <c r="B188" s="18">
-        <v>45981</v>
+        <v>45978</v>
       </c>
       <c r="C188" s="4">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="D188" s="10"/>
-      <c r="E188" s="19" t="s">
+      <c r="E188" s="20" t="s">
         <v>50</v>
       </c>
       <c r="F188" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="G188" s="19">
+      <c r="G188" s="4">
         <v>4</v>
       </c>
       <c r="H188" s="19">
-        <v>681.19</v>
+        <v>613.04999999999995</v>
       </c>
       <c r="I188" s="4" t="s">
         <v>93</v>
@@ -7321,26 +7321,26 @@
         <v>1</v>
       </c>
       <c r="B189" s="18">
-        <v>45981</v>
+        <v>45980</v>
       </c>
       <c r="C189" s="4">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D189" s="10"/>
-      <c r="E189" s="19" t="s">
-        <v>58</v>
+      <c r="E189" s="20" t="s">
+        <v>50</v>
       </c>
       <c r="F189" s="13" t="s">
         <v>90</v>
       </c>
       <c r="G189" s="19">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H189" s="19">
-        <v>3423</v>
+        <v>645</v>
       </c>
       <c r="I189" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="190" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -7348,23 +7348,23 @@
         <v>1</v>
       </c>
       <c r="B190" s="18">
-        <v>45975</v>
+        <v>45981</v>
       </c>
       <c r="C190" s="4">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="D190" s="10"/>
-      <c r="E190" s="4" t="s">
-        <v>47</v>
+      <c r="E190" s="19" t="s">
+        <v>50</v>
       </c>
       <c r="F190" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="G190" s="20">
-        <v>3</v>
+      <c r="G190" s="19">
+        <v>4</v>
       </c>
       <c r="H190" s="19">
-        <v>673</v>
+        <v>681.19</v>
       </c>
       <c r="I190" s="4" t="s">
         <v>93</v>
@@ -7375,26 +7375,26 @@
         <v>1</v>
       </c>
       <c r="B191" s="18">
-        <v>45975</v>
+        <v>45981</v>
       </c>
       <c r="C191" s="4">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="D191" s="10"/>
-      <c r="E191" s="4" t="s">
-        <v>47</v>
+      <c r="E191" s="19" t="s">
+        <v>58</v>
       </c>
       <c r="F191" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="G191" s="20">
-        <v>3</v>
+      <c r="G191" s="19">
+        <v>1</v>
       </c>
       <c r="H191" s="19">
-        <v>705</v>
+        <v>3423</v>
       </c>
       <c r="I191" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="192" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -7402,23 +7402,23 @@
         <v>1</v>
       </c>
       <c r="B192" s="18">
-        <v>45978</v>
+        <v>45975</v>
       </c>
       <c r="C192" s="4">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D192" s="10"/>
-      <c r="E192" s="20" t="s">
+      <c r="E192" s="4" t="s">
         <v>47</v>
       </c>
       <c r="F192" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="G192" s="4">
+      <c r="G192" s="20">
         <v>3</v>
       </c>
       <c r="H192" s="19">
-        <v>741</v>
+        <v>673</v>
       </c>
       <c r="I192" s="4" t="s">
         <v>93</v>
@@ -7429,23 +7429,23 @@
         <v>1</v>
       </c>
       <c r="B193" s="18">
-        <v>46057</v>
+        <v>45975</v>
       </c>
       <c r="C193" s="4">
-        <v>62</v>
+        <v>144</v>
       </c>
       <c r="D193" s="10"/>
-      <c r="E193" s="19" t="s">
+      <c r="E193" s="4" t="s">
         <v>47</v>
       </c>
       <c r="F193" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="G193" s="19">
+      <c r="G193" s="20">
         <v>3</v>
       </c>
       <c r="H193" s="19">
-        <v>778.55</v>
+        <v>705</v>
       </c>
       <c r="I193" s="4" t="s">
         <v>93</v>
@@ -7456,23 +7456,23 @@
         <v>1</v>
       </c>
       <c r="B194" s="18">
-        <v>46058</v>
+        <v>45978</v>
       </c>
       <c r="C194" s="4">
-        <v>61</v>
+        <v>141</v>
       </c>
       <c r="D194" s="10"/>
-      <c r="E194" s="19" t="s">
+      <c r="E194" s="20" t="s">
         <v>47</v>
       </c>
       <c r="F194" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="G194" s="19">
+      <c r="G194" s="4">
         <v>3</v>
       </c>
       <c r="H194" s="19">
-        <v>816.8</v>
+        <v>741</v>
       </c>
       <c r="I194" s="4" t="s">
         <v>93</v>
@@ -7483,23 +7483,23 @@
         <v>1</v>
       </c>
       <c r="B195" s="18">
-        <v>46027</v>
+        <v>46057</v>
       </c>
       <c r="C195" s="4">
-        <v>92</v>
+        <v>62</v>
       </c>
       <c r="D195" s="10"/>
       <c r="E195" s="19" t="s">
-        <v>109</v>
+        <v>47</v>
       </c>
       <c r="F195" s="13" t="s">
         <v>90</v>
       </c>
       <c r="G195" s="19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H195" s="19">
-        <v>947.97</v>
+        <v>778.55</v>
       </c>
       <c r="I195" s="4" t="s">
         <v>93</v>
@@ -7510,23 +7510,23 @@
         <v>1</v>
       </c>
       <c r="B196" s="18">
-        <v>46080</v>
+        <v>46058</v>
       </c>
       <c r="C196" s="4">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="D196" s="10"/>
       <c r="E196" s="19" t="s">
-        <v>109</v>
+        <v>47</v>
       </c>
       <c r="F196" s="13" t="s">
         <v>90</v>
       </c>
       <c r="G196" s="19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H196" s="19">
-        <v>994.35</v>
+        <v>816.8</v>
       </c>
       <c r="I196" s="4" t="s">
         <v>93</v>
@@ -7537,23 +7537,23 @@
         <v>1</v>
       </c>
       <c r="B197" s="18">
-        <v>46015</v>
+        <v>46027</v>
       </c>
       <c r="C197" s="4">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="D197" s="10"/>
       <c r="E197" s="19" t="s">
-        <v>89</v>
+        <v>109</v>
       </c>
       <c r="F197" s="13" t="s">
         <v>90</v>
       </c>
       <c r="G197" s="19">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H197" s="19">
-        <v>244.89</v>
+        <v>947.97</v>
       </c>
       <c r="I197" s="4" t="s">
         <v>93</v>
@@ -7564,23 +7564,23 @@
         <v>1</v>
       </c>
       <c r="B198" s="18">
-        <v>46024</v>
+        <v>46080</v>
       </c>
       <c r="C198" s="4">
-        <v>95</v>
+        <v>39</v>
       </c>
       <c r="D198" s="10"/>
       <c r="E198" s="19" t="s">
-        <v>89</v>
+        <v>109</v>
       </c>
       <c r="F198" s="13" t="s">
         <v>90</v>
       </c>
       <c r="G198" s="19">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H198" s="19">
-        <v>257.44</v>
+        <v>994.35</v>
       </c>
       <c r="I198" s="4" t="s">
         <v>93</v>
@@ -7591,23 +7591,23 @@
         <v>1</v>
       </c>
       <c r="B199" s="18">
-        <v>45988</v>
+        <v>46015</v>
       </c>
       <c r="C199" s="4">
-        <v>131</v>
+        <v>104</v>
       </c>
       <c r="D199" s="10"/>
       <c r="E199" s="19" t="s">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="F199" s="13" t="s">
         <v>90</v>
       </c>
       <c r="G199" s="19">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H199" s="19">
-        <v>1758.1</v>
+        <v>244.89</v>
       </c>
       <c r="I199" s="4" t="s">
         <v>93</v>
@@ -7625,16 +7625,16 @@
       </c>
       <c r="D200" s="10"/>
       <c r="E200" s="19" t="s">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="F200" s="13" t="s">
         <v>90</v>
       </c>
       <c r="G200" s="19">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H200" s="19">
-        <v>1846.5</v>
+        <v>257.44</v>
       </c>
       <c r="I200" s="4" t="s">
         <v>93</v>
@@ -7645,10 +7645,10 @@
         <v>1</v>
       </c>
       <c r="B201" s="18">
-        <v>46027</v>
+        <v>45988</v>
       </c>
       <c r="C201" s="4">
-        <v>92</v>
+        <v>131</v>
       </c>
       <c r="D201" s="10"/>
       <c r="E201" s="19" t="s">
@@ -7661,7 +7661,7 @@
         <v>1</v>
       </c>
       <c r="H201" s="19">
-        <v>1939</v>
+        <v>1758.1</v>
       </c>
       <c r="I201" s="4" t="s">
         <v>93</v>
@@ -7672,10 +7672,10 @@
         <v>1</v>
       </c>
       <c r="B202" s="18">
-        <v>46034</v>
+        <v>46024</v>
       </c>
       <c r="C202" s="4">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="D202" s="10"/>
       <c r="E202" s="19" t="s">
@@ -7688,7 +7688,7 @@
         <v>1</v>
       </c>
       <c r="H202" s="19">
-        <v>1798.83</v>
+        <v>1846.5</v>
       </c>
       <c r="I202" s="4" t="s">
         <v>93</v>
@@ -7699,10 +7699,10 @@
         <v>1</v>
       </c>
       <c r="B203" s="18">
-        <v>46063</v>
+        <v>46027</v>
       </c>
       <c r="C203" s="4">
-        <v>56</v>
+        <v>92</v>
       </c>
       <c r="D203" s="10"/>
       <c r="E203" s="19" t="s">
@@ -7715,7 +7715,7 @@
         <v>1</v>
       </c>
       <c r="H203" s="19">
-        <v>2064.9</v>
+        <v>1939</v>
       </c>
       <c r="I203" s="4" t="s">
         <v>93</v>
@@ -7725,11 +7725,11 @@
       <c r="A204" s="14">
         <v>1</v>
       </c>
-      <c r="B204" s="23">
-        <v>46064</v>
+      <c r="B204" s="18">
+        <v>46034</v>
       </c>
       <c r="C204" s="4">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="D204" s="10"/>
       <c r="E204" s="19" t="s">
@@ -7742,7 +7742,7 @@
         <v>1</v>
       </c>
       <c r="H204" s="19">
-        <v>2138</v>
+        <v>1798.83</v>
       </c>
       <c r="I204" s="4" t="s">
         <v>93</v>
@@ -7753,10 +7753,10 @@
         <v>1</v>
       </c>
       <c r="B205" s="18">
-        <v>46072</v>
+        <v>46063</v>
       </c>
       <c r="C205" s="4">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="D205" s="10"/>
       <c r="E205" s="19" t="s">
@@ -7769,7 +7769,7 @@
         <v>1</v>
       </c>
       <c r="H205" s="19">
-        <v>2248</v>
+        <v>2064.9</v>
       </c>
       <c r="I205" s="4" t="s">
         <v>93</v>
@@ -7779,11 +7779,11 @@
       <c r="A206" s="14">
         <v>1</v>
       </c>
-      <c r="B206" s="18">
-        <v>46077</v>
+      <c r="B206" s="23">
+        <v>46064</v>
       </c>
       <c r="C206" s="4">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="D206" s="10"/>
       <c r="E206" s="19" t="s">
@@ -7796,7 +7796,7 @@
         <v>1</v>
       </c>
       <c r="H206" s="19">
-        <v>2356.9</v>
+        <v>2138</v>
       </c>
       <c r="I206" s="4" t="s">
         <v>93</v>
@@ -7807,23 +7807,23 @@
         <v>1</v>
       </c>
       <c r="B207" s="18">
-        <v>45967</v>
+        <v>46072</v>
       </c>
       <c r="C207" s="4">
-        <v>152</v>
+        <v>47</v>
       </c>
       <c r="D207" s="10"/>
       <c r="E207" s="19" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="F207" s="13" t="s">
         <v>90</v>
       </c>
       <c r="G207" s="19">
-        <v>99</v>
+        <v>1</v>
       </c>
       <c r="H207" s="19">
-        <v>25.3</v>
+        <v>2248</v>
       </c>
       <c r="I207" s="4" t="s">
         <v>93</v>
@@ -7834,23 +7834,23 @@
         <v>1</v>
       </c>
       <c r="B208" s="18">
-        <v>45981</v>
+        <v>46077</v>
       </c>
       <c r="C208" s="4">
-        <v>138</v>
+        <v>42</v>
       </c>
       <c r="D208" s="10"/>
       <c r="E208" s="19" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="F208" s="13" t="s">
         <v>90</v>
       </c>
       <c r="G208" s="19">
-        <v>98</v>
+        <v>1</v>
       </c>
       <c r="H208" s="19">
-        <v>26.6</v>
+        <v>2356.9</v>
       </c>
       <c r="I208" s="4" t="s">
         <v>93</v>
@@ -7861,23 +7861,23 @@
         <v>1</v>
       </c>
       <c r="B209" s="18">
-        <v>46006</v>
+        <v>45967</v>
       </c>
       <c r="C209" s="4">
-        <v>113</v>
+        <v>152</v>
       </c>
       <c r="D209" s="10"/>
-      <c r="E209" s="20" t="s">
+      <c r="E209" s="19" t="s">
         <v>61</v>
       </c>
       <c r="F209" s="13" t="s">
         <v>90</v>
       </c>
       <c r="G209" s="19">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="H209" s="19">
-        <v>28</v>
+        <v>25.3</v>
       </c>
       <c r="I209" s="4" t="s">
         <v>93</v>
@@ -7888,10 +7888,10 @@
         <v>1</v>
       </c>
       <c r="B210" s="18">
-        <v>46044</v>
+        <v>45981</v>
       </c>
       <c r="C210" s="4">
-        <v>1</v>
+        <v>138</v>
       </c>
       <c r="D210" s="10"/>
       <c r="E210" s="19" t="s">
@@ -7901,10 +7901,10 @@
         <v>90</v>
       </c>
       <c r="G210" s="19">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="H210" s="19">
-        <v>29.4</v>
+        <v>26.6</v>
       </c>
       <c r="I210" s="4" t="s">
         <v>93</v>
@@ -7915,23 +7915,23 @@
         <v>1</v>
       </c>
       <c r="B211" s="18">
-        <v>46059</v>
+        <v>46006</v>
       </c>
       <c r="C211" s="4">
-        <v>60</v>
+        <v>113</v>
       </c>
       <c r="D211" s="10"/>
-      <c r="E211" s="19" t="s">
+      <c r="E211" s="20" t="s">
         <v>61</v>
       </c>
       <c r="F211" s="13" t="s">
         <v>90</v>
       </c>
       <c r="G211" s="19">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="H211" s="19">
-        <v>30.85</v>
+        <v>28</v>
       </c>
       <c r="I211" s="4" t="s">
         <v>93</v>
@@ -7942,10 +7942,10 @@
         <v>1</v>
       </c>
       <c r="B212" s="18">
-        <v>46077</v>
+        <v>46044</v>
       </c>
       <c r="C212" s="4">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="D212" s="10"/>
       <c r="E212" s="19" t="s">
@@ -7958,7 +7958,7 @@
         <v>85</v>
       </c>
       <c r="H212" s="19">
-        <v>32.4</v>
+        <v>29.4</v>
       </c>
       <c r="I212" s="4" t="s">
         <v>93</v>
@@ -7969,23 +7969,23 @@
         <v>1</v>
       </c>
       <c r="B213" s="18">
-        <v>45981</v>
+        <v>46059</v>
       </c>
       <c r="C213" s="4">
-        <v>138</v>
+        <v>60</v>
       </c>
       <c r="D213" s="10"/>
       <c r="E213" s="19" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F213" s="13" t="s">
         <v>90</v>
       </c>
       <c r="G213" s="19">
-        <v>3</v>
+        <v>85</v>
       </c>
       <c r="H213" s="19">
-        <v>831.9</v>
+        <v>30.85</v>
       </c>
       <c r="I213" s="4" t="s">
         <v>93</v>
@@ -7996,23 +7996,23 @@
         <v>1</v>
       </c>
       <c r="B214" s="18">
-        <v>46027</v>
+        <v>46077</v>
       </c>
       <c r="C214" s="4">
-        <v>92</v>
+        <v>42</v>
       </c>
       <c r="D214" s="10"/>
       <c r="E214" s="19" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F214" s="13" t="s">
         <v>90</v>
       </c>
       <c r="G214" s="19">
-        <v>3</v>
+        <v>85</v>
       </c>
       <c r="H214" s="19">
-        <v>873.5</v>
+        <v>32.4</v>
       </c>
       <c r="I214" s="4" t="s">
         <v>93</v>
@@ -8023,23 +8023,23 @@
         <v>1</v>
       </c>
       <c r="B215" s="18">
-        <v>46029</v>
+        <v>45981</v>
       </c>
       <c r="C215" s="4">
-        <v>90</v>
+        <v>138</v>
       </c>
       <c r="D215" s="10"/>
       <c r="E215" s="19" t="s">
-        <v>112</v>
+        <v>60</v>
       </c>
       <c r="F215" s="13" t="s">
         <v>90</v>
       </c>
       <c r="G215" s="19">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H215" s="19">
-        <v>426</v>
+        <v>831.9</v>
       </c>
       <c r="I215" s="4" t="s">
         <v>93</v>
@@ -8050,23 +8050,23 @@
         <v>1</v>
       </c>
       <c r="B216" s="18">
-        <v>46029</v>
+        <v>46027</v>
       </c>
       <c r="C216" s="4">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D216" s="10"/>
       <c r="E216" s="19" t="s">
-        <v>112</v>
+        <v>60</v>
       </c>
       <c r="F216" s="13" t="s">
         <v>90</v>
       </c>
       <c r="G216" s="19">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H216" s="19">
-        <v>448.15</v>
+        <v>873.5</v>
       </c>
       <c r="I216" s="4" t="s">
         <v>93</v>
@@ -8077,23 +8077,23 @@
         <v>1</v>
       </c>
       <c r="B217" s="18">
-        <v>46027</v>
+        <v>46029</v>
       </c>
       <c r="C217" s="4">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D217" s="10"/>
       <c r="E217" s="19" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="F217" s="13" t="s">
         <v>90</v>
       </c>
       <c r="G217" s="19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H217" s="19">
-        <v>389.14</v>
+        <v>426</v>
       </c>
       <c r="I217" s="4" t="s">
         <v>93</v>
@@ -8104,23 +8104,23 @@
         <v>1</v>
       </c>
       <c r="B218" s="18">
-        <v>46062</v>
+        <v>46029</v>
       </c>
       <c r="C218" s="4">
-        <v>57</v>
+        <v>90</v>
       </c>
       <c r="D218" s="10"/>
       <c r="E218" s="19" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="F218" s="13" t="s">
         <v>90</v>
       </c>
       <c r="G218" s="19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H218" s="19">
-        <v>397.25</v>
+        <v>448.15</v>
       </c>
       <c r="I218" s="4" t="s">
         <v>93</v>
@@ -8131,10 +8131,10 @@
         <v>1</v>
       </c>
       <c r="B219" s="18">
-        <v>46062</v>
+        <v>46027</v>
       </c>
       <c r="C219" s="4">
-        <v>57</v>
+        <v>92</v>
       </c>
       <c r="D219" s="10"/>
       <c r="E219" s="19" t="s">
@@ -8144,10 +8144,10 @@
         <v>90</v>
       </c>
       <c r="G219" s="19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H219" s="19">
-        <v>418</v>
+        <v>389.14</v>
       </c>
       <c r="I219" s="4" t="s">
         <v>93</v>
@@ -8157,11 +8157,11 @@
       <c r="A220" s="14">
         <v>1</v>
       </c>
-      <c r="B220" s="23">
-        <v>46064</v>
+      <c r="B220" s="18">
+        <v>46062</v>
       </c>
       <c r="C220" s="4">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D220" s="10"/>
       <c r="E220" s="19" t="s">
@@ -8174,7 +8174,7 @@
         <v>6</v>
       </c>
       <c r="H220" s="19">
-        <v>438</v>
+        <v>397.25</v>
       </c>
       <c r="I220" s="4" t="s">
         <v>93</v>
@@ -8184,14 +8184,14 @@
       <c r="A221" s="14">
         <v>1</v>
       </c>
-      <c r="B221" s="22">
-        <v>46079</v>
+      <c r="B221" s="18">
+        <v>46062</v>
       </c>
       <c r="C221" s="4">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="D221" s="10"/>
-      <c r="E221" s="27" t="s">
+      <c r="E221" s="19" t="s">
         <v>107</v>
       </c>
       <c r="F221" s="13" t="s">
@@ -8201,7 +8201,7 @@
         <v>6</v>
       </c>
       <c r="H221" s="19">
-        <v>460.15</v>
+        <v>418</v>
       </c>
       <c r="I221" s="4" t="s">
         <v>93</v>
@@ -8211,11 +8211,11 @@
       <c r="A222" s="14">
         <v>1</v>
       </c>
-      <c r="B222" s="18">
-        <v>46106</v>
+      <c r="B222" s="23">
+        <v>46064</v>
       </c>
       <c r="C222" s="4">
-        <v>1</v>
+        <v>55</v>
       </c>
       <c r="D222" s="10"/>
       <c r="E222" s="19" t="s">
@@ -8228,7 +8228,7 @@
         <v>6</v>
       </c>
       <c r="H222" s="19">
-        <v>483.3</v>
+        <v>438</v>
       </c>
       <c r="I222" s="4" t="s">
         <v>93</v>
@@ -8238,14 +8238,14 @@
       <c r="A223" s="14">
         <v>1</v>
       </c>
-      <c r="B223" s="18">
-        <v>46111</v>
+      <c r="B223" s="22">
+        <v>46079</v>
       </c>
       <c r="C223" s="4">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="D223" s="10"/>
-      <c r="E223" s="19" t="s">
+      <c r="E223" s="27" t="s">
         <v>107</v>
       </c>
       <c r="F223" s="13" t="s">
@@ -8255,7 +8255,7 @@
         <v>6</v>
       </c>
       <c r="H223" s="19">
-        <v>485</v>
+        <v>460.15</v>
       </c>
       <c r="I223" s="4" t="s">
         <v>93</v>
@@ -8266,7 +8266,7 @@
         <v>1</v>
       </c>
       <c r="B224" s="18">
-        <v>46114</v>
+        <v>46106</v>
       </c>
       <c r="C224" s="4">
         <v>1</v>
@@ -8282,7 +8282,7 @@
         <v>6</v>
       </c>
       <c r="H224" s="19">
-        <v>507.15</v>
+        <v>483.3</v>
       </c>
       <c r="I224" s="4" t="s">
         <v>93</v>
@@ -8293,7 +8293,7 @@
         <v>1</v>
       </c>
       <c r="B225" s="18">
-        <v>46118</v>
+        <v>46114</v>
       </c>
       <c r="C225" s="4">
         <v>1</v>
@@ -8309,7 +8309,7 @@
         <v>6</v>
       </c>
       <c r="H225" s="19">
-        <v>508</v>
+        <v>507.15</v>
       </c>
       <c r="I225" s="4" t="s">
         <v>93</v>
@@ -10329,7 +10329,7 @@
         <v>131</v>
       </c>
       <c r="D302" s="18"/>
-      <c r="E302" s="19" t="s">
+      <c r="E302" s="37" t="s">
         <v>70</v>
       </c>
       <c r="F302" s="13" t="s">
@@ -10358,16 +10358,16 @@
         <v>117</v>
       </c>
       <c r="D303" s="18"/>
-      <c r="E303" s="37" t="s">
+      <c r="E303" s="19" t="s">
         <v>70</v>
       </c>
       <c r="F303" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="G303" s="19">
+      <c r="G303" s="40">
         <v>4</v>
       </c>
-      <c r="H303" s="19">
+      <c r="H303" s="37">
         <v>808</v>
       </c>
       <c r="I303" s="4" t="s">
@@ -10393,10 +10393,10 @@
       <c r="F304" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="G304" s="40">
+      <c r="G304" s="19">
         <v>3</v>
       </c>
-      <c r="H304" s="37">
+      <c r="H304" s="19">
         <v>767</v>
       </c>
       <c r="I304" s="4" t="s">
@@ -10503,7 +10503,7 @@
         <v>56</v>
       </c>
       <c r="D308" s="18"/>
-      <c r="E308" s="19" t="s">
+      <c r="E308" s="37" t="s">
         <v>128</v>
       </c>
       <c r="F308" s="13" t="s">
@@ -10532,7 +10532,7 @@
         <v>50</v>
       </c>
       <c r="D309" s="18"/>
-      <c r="E309" s="19" t="s">
+      <c r="E309" s="37" t="s">
         <v>128</v>
       </c>
       <c r="F309" s="13" t="s">
